--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EAC88DE-BCE3-44A2-A2D0-E873F74DF1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133C48D8-BAFA-4616-8751-D97327323CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="527">
   <si>
     <t>需求 ID</t>
   </si>
@@ -45,9 +45,6 @@
     <t>需求描述</t>
   </si>
   <si>
-    <t>关联风险 ID</t>
-  </si>
-  <si>
     <t>风险描述</t>
   </si>
   <si>
@@ -57,39 +54,24 @@
     <t>REQ-M1</t>
   </si>
   <si>
-    <t>迁移单个老动态到HBase</t>
-  </si>
-  <si>
     <t>RSK-1.1.001</t>
   </si>
   <si>
-    <t>HBase写入失败或验证失败导致迁移中断</t>
-  </si>
-  <si>
     <t>P0</t>
   </si>
   <si>
     <t>RSK-1.1.002</t>
   </si>
   <si>
-    <t>HBase写入成功但MySQL删除失败，导致冷热数据重复</t>
-  </si>
-  <si>
     <t>P2</t>
   </si>
   <si>
     <t>RSK-1.2.001</t>
   </si>
   <si>
-    <t>冷迁移时HBase写入失败，同时MySQL错误删除所有数据</t>
-  </si>
-  <si>
     <t>RSK-1.2.002</t>
   </si>
   <si>
-    <t>HBase未写入评论/点赞数据，MySQL已删除导致数据丢失</t>
-  </si>
-  <si>
     <t>REQ-M2</t>
   </si>
   <si>
@@ -99,18 +81,12 @@
     <t>RSK-1.1.004</t>
   </si>
   <si>
-    <t>超过评论阈值未恢复NONE，无法再次进入迁移流程</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
     <t>RSK-1.4.001</t>
   </si>
   <si>
-    <t>超过阈值恢复至NONE操作失败，帖子被锁定24小时</t>
-  </si>
-  <si>
     <t>REQ-M3-A</t>
   </si>
   <si>
@@ -120,9 +96,6 @@
     <t>RSK-1.3.004</t>
   </si>
   <si>
-    <t>MIGRATING帖子在列表中隐形，用户无法发现</t>
-  </si>
-  <si>
     <t>REQ-M3-B</t>
   </si>
   <si>
@@ -150,39 +123,21 @@
     <t>RSK-1.2.003</t>
   </si>
   <si>
-    <t>恢复时HBase读取失败，冷数据无法完整恢复</t>
-  </si>
-  <si>
     <t>RSK-1.2.004</t>
   </si>
   <si>
-    <t>恢复时MySQL插入成功但评论/点赞插入失败</t>
-  </si>
-  <si>
     <t>RSK-1.3.006</t>
   </si>
   <si>
-    <t>恢复过程中HBase读取异常，动态恢复但评论/点赞丢失</t>
-  </si>
-  <si>
     <t>RSK-1.3.007</t>
   </si>
   <si>
-    <t>恢复后动态状态未正确设置为NONE，恢复后仍隐形</t>
-  </si>
-  <si>
     <t>RSK-1.4.003</t>
   </si>
   <si>
-    <t>用户查询触发恢复与定时任务重试并发导致冲突</t>
-  </si>
-  <si>
     <t>RSK-1.5.002</t>
   </si>
   <si>
-    <t>用户点击激活时MQ恢复事件发送或处理失败</t>
-  </si>
-  <si>
     <t>REQ-M5</t>
   </si>
   <si>
@@ -201,24 +156,12 @@
     <t>RSK-1.1.003</t>
   </si>
   <si>
-    <t>MIGRATING状态遗留后未正确重试，数据既不在热库也未迁移</t>
-  </si>
-  <si>
     <t>RSK-1.4.002</t>
   </si>
   <si>
-    <t>定时任务执行失败，MIGRATING遗留数据无法重试</t>
-  </si>
-  <si>
     <t>REQ-M7</t>
   </si>
   <si>
-    <t>访问冷动态的查询回源</t>
-  </si>
-  <si>
-    <t>HBase宕机时冷动态查询请求直接失败</t>
-  </si>
-  <si>
     <t>状态转移表 (STT)</t>
   </si>
   <si>
@@ -255,9 +198,6 @@
     <t>M-1</t>
   </si>
   <si>
-    <t>用户删除</t>
-  </si>
-  <si>
     <t>鉴权通过</t>
   </si>
   <si>
@@ -876,54 +816,27 @@
     <t>REQ-M1-S</t>
   </si>
   <si>
-    <t>已通过审核的动态 7 天迁移，未通过的动态 3 天迁移</t>
-  </si>
-  <si>
     <t>RSK-1.1.005</t>
   </si>
   <si>
-    <t>状态判断逻辑错误，导致新发布的 PENDING 动态被误迁移或者迁移时间判断错误</t>
-  </si>
-  <si>
     <t>REQ-M3-C</t>
   </si>
   <si>
     <t>RSK-1.3.010</t>
   </si>
   <si>
-    <t>未通过审核的内容被他人通过接口或列表查询获取</t>
-  </si>
-  <si>
     <t>RSK-1.3.009</t>
   </si>
   <si>
-    <t>恢复过程中审核状态发生变更，导致数据状态机冲突或逻辑违例</t>
-  </si>
-  <si>
-    <t>迁移中动态拒绝评论/点赞/修改</t>
-  </si>
-  <si>
-    <t>MIGRATING动态仍被允许加载/评论/点赞/修改</t>
-  </si>
-  <si>
     <t>REQ-M8</t>
   </si>
   <si>
-    <t>仅 migration_status 为 NONE 时允许更新审核状态</t>
-  </si>
-  <si>
     <t>RSK-1.3.008</t>
   </si>
   <si>
-    <t>迁移中动态被修改审核状态，导致状态机冲突或数据不一致</t>
-  </si>
-  <si>
     <t>REQ-M9</t>
   </si>
   <si>
-    <t>各状态下的动态彻底删除</t>
-  </si>
-  <si>
     <t>RSK-1.2.005</t>
   </si>
   <si>
@@ -933,13 +846,7 @@
     <t>REQ-M10</t>
   </si>
   <si>
-    <t>用户修改动态内容后，无论原状态，一律变回 PENDING (审核中)</t>
-  </si>
-  <si>
     <t>RSK-1.3.011</t>
-  </si>
-  <si>
-    <t>修改内容后状态未及时回滚，导致违规内容跳过审核直接公开</t>
   </si>
   <si>
     <t>NONE (PENDING)</t>
@@ -2447,6 +2354,116 @@
   </si>
   <si>
     <t>状态为 PENDING的动态不可见</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风险 ID</t>
+  </si>
+  <si>
+    <t>Tech Risk</t>
+  </si>
+  <si>
+    <t>Bus. Risk</t>
+  </si>
+  <si>
+    <t>Risk Pri. #</t>
+  </si>
+  <si>
+    <t>迁移单个老动态到 HBase</t>
+  </si>
+  <si>
+    <t>HBase 写入失败或验证失败导致迁移中断</t>
+  </si>
+  <si>
+    <t>HBase 写入成功但 MySQL 删除失败，导致冷热数据重复</t>
+  </si>
+  <si>
+    <t>冷迁移时 HBase 写入失败，同时 MySQL 错误删除所有数据</t>
+  </si>
+  <si>
+    <t>HBase 未写入评论/点赞数据，MySQL 已删除导致数据丢失</t>
+  </si>
+  <si>
+    <t>动态按审核状态分阶梯迁移</t>
+  </si>
+  <si>
+    <t>状态判断逻辑错误，导致 PENDING 动态误迁移或时间错误</t>
+  </si>
+  <si>
+    <t>超过评论阈值未恢复 NONE，无法再次进入迁移流程</t>
+  </si>
+  <si>
+    <t>超过阈值恢复至 NONE 操作失败，帖子被锁定 24 小时</t>
+  </si>
+  <si>
+    <t>MIGRATING 帖子在列表中隐形，用户无法发现</t>
+  </si>
+  <si>
+    <t>未通过审核内容被他人通过接口或列表查询获取</t>
+  </si>
+  <si>
+    <t>恢复时 HBase 读取失败，冷数据无法完整恢复</t>
+  </si>
+  <si>
+    <t>恢复时 MySQL 插入成功但评论/点赞插入失败</t>
+  </si>
+  <si>
+    <t>恢复过程中 HBase 读取异常，动态恢复但相关数据丢失</t>
+  </si>
+  <si>
+    <t>恢复后状态未正确设为 NONE，导致动态仍隐形</t>
+  </si>
+  <si>
+    <t>用户查询触发恢复与定时任务重试并发冲突</t>
+  </si>
+  <si>
+    <t>用户点击激活时 MQ 恢复事件发送或处理失败</t>
+  </si>
+  <si>
+    <t>恢复过程中审核状态变更，导致状态机冲突</t>
+  </si>
+  <si>
+    <t>MIGRATING 动态仍被允许加载/评论/点赞/修改</t>
+  </si>
+  <si>
+    <t>状态遗留后未重试，数据在冷热库间“失踪”</t>
+  </si>
+  <si>
+    <t>定时任务执行失败，遗留数据无法自动重试</t>
+  </si>
+  <si>
+    <t>访问冷动态查询回源</t>
+  </si>
+  <si>
+    <t>HBase 宕机时冷动态查询请求直接失败</t>
+  </si>
+  <si>
+    <t>NONE 状态才允许更新审核</t>
+  </si>
+  <si>
+    <t>迁移中状态被修改，导致数据不一致或逻辑违例</t>
+  </si>
+  <si>
+    <t>彻底删除动态</t>
+  </si>
+  <si>
+    <t>用户删除</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>迁移中拒绝点赞/评论/修改操作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户修改动态内容</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改后审核状态未及时回退，违规内容绕过审核公开</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅通过审核的内容对他人可见</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2545,7 +2562,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2730,11 +2747,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2803,6 +2844,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3107,484 +3157,758 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="4" max="4" width="46.6328125" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="B2" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="D2" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="F2" s="14">
+        <v>3</v>
+      </c>
+      <c r="G2" s="14">
+        <v>4</v>
+      </c>
+      <c r="H2" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D3" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F3" s="14">
+        <v>3</v>
+      </c>
+      <c r="G3" s="14">
+        <v>2</v>
+      </c>
+      <c r="H3" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="D4" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="14">
+        <v>4</v>
+      </c>
+      <c r="G4" s="14">
         <v>5</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="H4" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="F5" s="14">
+        <v>4</v>
+      </c>
+      <c r="G5" s="14">
+        <v>5</v>
+      </c>
+      <c r="H5" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="14">
+        <v>3</v>
+      </c>
+      <c r="G6" s="14">
+        <v>4</v>
+      </c>
+      <c r="H6" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="14">
+        <v>2</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="14">
+        <v>3</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="14">
+        <v>4</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="14">
+        <v>4</v>
+      </c>
+      <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14">
+        <v>3</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="14">
+        <v>3</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="14">
+        <v>4</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="14">
+        <v>3</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="14">
+        <v>5</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="14">
+        <v>3</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="14">
+        <v>4</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="14">
+        <v>4</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3</v>
+      </c>
+      <c r="H21" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="14">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
         <v>10</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+    </row>
+    <row r="25" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="14">
+        <v>4</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="14">
+        <v>2</v>
+      </c>
+      <c r="G26" s="14">
+        <v>1</v>
+      </c>
+      <c r="H26" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="28" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="25">
+        <v>3</v>
+      </c>
+      <c r="G27" s="25">
         <v>5</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="H27" s="25">
         <v>15</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>291</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>300</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3593,324 +3917,324 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>323</v>
+        <v>292</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>72</v>
+        <v>522</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>333</v>
+        <v>302</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>338</v>
+        <v>307</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>339</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -3922,163 +4246,163 @@
     </row>
     <row r="20" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -4090,159 +4414,429 @@
     </row>
     <row r="27" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="F27" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="G27" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>95</v>
-      </c>
       <c r="H27" s="19" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="B29" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>95</v>
-      </c>
       <c r="D29" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="B30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="F30" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>95</v>
-      </c>
       <c r="H30" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="B31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>95</v>
-      </c>
       <c r="G31" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>95</v>
-      </c>
       <c r="G32" s="19" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>75</v>
-      </c>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="24"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="24"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="24"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="24"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="24"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="24"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="24"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="24"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -4264,478 +4858,478 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
       <c r="D4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>372</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>373</v>
+        <v>342</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>374</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>378</v>
+        <v>347</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>383</v>
+        <v>352</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>384</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4758,562 +5352,562 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>433</v>
+        <v>402</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>379</v>
+        <v>348</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>521</v>
+        <v>490</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>520</v>
+        <v>489</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>522</v>
+        <v>491</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>491</v>
+        <v>460</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>493</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>497</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>497</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -5334,461 +5928,461 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" s="5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5811,42 +6405,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="84" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -5868,44 +6462,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5916,86 +6510,86 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6006,58 +6600,58 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6068,58 +6662,58 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6130,58 +6724,58 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -6192,16 +6786,16 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -6212,73 +6806,73 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D34" s="8"/>
     </row>
@@ -6290,109 +6884,109 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="D43" s="8"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="D44" s="8"/>
     </row>
@@ -6404,61 +6998,61 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="D50" s="8"/>
     </row>
@@ -6470,73 +7064,73 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="D52" s="8"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="D53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="D57" s="8"/>
     </row>
@@ -6548,25 +7142,25 @@
     </row>
     <row r="59" spans="1:4" ht="28" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="D59" s="8"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="D60" s="8"/>
     </row>
@@ -6578,73 +7172,73 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="D64" s="8"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="D65" s="8"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="D66" s="8"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="D67" s="8"/>
     </row>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133C48D8-BAFA-4616-8751-D97327323CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="缺陷报告" sheetId="7" r:id="rId6"/>
     <sheet name="ID说明与列名解释" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="532">
   <si>
     <t>需求 ID</t>
   </si>
@@ -495,9 +494,6 @@
     <t>测试通过: 系统检测到上次迁移失败的遗留数据，继续迁移。HBase中已存在数据(幂等跳过)，开始删除MySQL数据</t>
   </si>
   <si>
-    <t>已修复，所有9个核心单元测试全部通过</t>
-  </si>
-  <si>
     <t>ID类型</t>
   </si>
   <si>
@@ -559,9 +555,6 @@
   </si>
   <si>
     <t>1.4.xxx</t>
-  </si>
-  <si>
-    <t>System Stability(系统稳定性)</t>
   </si>
   <si>
     <t>RSK-1.4.001: 状态锁定</t>
@@ -2466,12 +2459,40 @@
     <t>仅通过审核的内容对他人可见</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>风险类别</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data Consistency(数据一致性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data Integrity(数据完整性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>System Stability(系统稳定性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Functionality &amp; Availability(功能可用性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Concurrency Control(并发控制)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>已修复，所有核心单元测试全部通过</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2552,6 +2573,14 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2775,7 +2804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2855,9 +2884,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3156,18 +3188,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="46.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="4" max="4" width="42.6328125" customWidth="1"/>
+    <col min="5" max="5" width="56.36328125" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -3175,389 +3208,434 @@
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>493</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>497</v>
+        <v>526</v>
       </c>
       <c r="E2" s="14" t="s">
+        <v>495</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="14">
+      <c r="G2" s="14">
         <v>3</v>
       </c>
-      <c r="G2" s="14">
+      <c r="H2" s="14">
         <v>4</v>
       </c>
-      <c r="H2" s="14">
+      <c r="I2" s="14">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="14">
+        <v>3</v>
+      </c>
+      <c r="H3" s="14">
+        <v>2</v>
+      </c>
+      <c r="I3" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="14">
+        <v>3</v>
+      </c>
+      <c r="H4" s="14">
+        <v>4</v>
+      </c>
+      <c r="I4" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="14">
+        <v>2</v>
+      </c>
+      <c r="H5" s="14">
+        <v>3</v>
+      </c>
+      <c r="I5" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="14">
+        <v>3</v>
+      </c>
+      <c r="H6" s="14">
+        <v>4</v>
+      </c>
+      <c r="I6" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>5</v>
+      </c>
+      <c r="I7" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="14">
-        <v>3</v>
-      </c>
-      <c r="G3" s="14">
-        <v>2</v>
-      </c>
-      <c r="H3" s="14">
+      <c r="F8" s="14" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>499</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="14">
-        <v>4</v>
-      </c>
-      <c r="G4" s="14">
-        <v>5</v>
-      </c>
-      <c r="H4" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="14">
-        <v>4</v>
-      </c>
-      <c r="G5" s="14">
-        <v>5</v>
-      </c>
-      <c r="H5" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>502</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="14">
-        <v>3</v>
-      </c>
-      <c r="G6" s="14">
-        <v>4</v>
-      </c>
-      <c r="H6" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="14">
-        <v>2</v>
-      </c>
-      <c r="G7" s="14">
-        <v>3</v>
-      </c>
-      <c r="H7" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="14">
-        <v>2</v>
       </c>
       <c r="G8" s="14">
         <v>4</v>
       </c>
       <c r="H8" s="14">
+        <v>5</v>
+      </c>
+      <c r="I8" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="14">
+        <v>3</v>
+      </c>
+      <c r="H9" s="14">
+        <v>5</v>
+      </c>
+      <c r="I9" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="14">
+        <v>4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>4</v>
+      </c>
+      <c r="I10" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="E9" s="14" t="s">
+      <c r="G11" s="14">
+        <v>2</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="14">
+      <c r="G12" s="14">
         <v>3</v>
       </c>
-      <c r="G9" s="14">
+      <c r="H12" s="14">
         <v>4</v>
       </c>
-      <c r="H9" s="14">
+      <c r="I12" s="14">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+    <row r="13" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D13" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="F13" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="14">
+      <c r="G13" s="14">
         <v>4</v>
       </c>
-      <c r="G10" s="14">
+      <c r="H13" s="14">
         <v>3</v>
       </c>
-      <c r="H10" s="14">
+      <c r="I13" s="14">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="14" t="s">
+    <row r="14" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="F11" s="14">
-        <v>4</v>
-      </c>
-      <c r="G11" s="14">
-        <v>3</v>
-      </c>
-      <c r="H11" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="14">
-        <v>3</v>
-      </c>
-      <c r="G12" s="14">
-        <v>5</v>
-      </c>
-      <c r="H12" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="14">
-        <v>3</v>
-      </c>
-      <c r="G13" s="14">
-        <v>5</v>
-      </c>
-      <c r="H13" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="14">
-        <v>4</v>
       </c>
       <c r="G14" s="14">
         <v>4</v>
       </c>
       <c r="H14" s="14">
+        <v>3</v>
+      </c>
+      <c r="I14" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>25</v>
-      </c>
       <c r="B15" s="14" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>509</v>
+        <v>170</v>
       </c>
       <c r="E15" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="14">
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
-      <c r="H15" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>25</v>
       </c>
@@ -3565,25 +3643,28 @@
         <v>26</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>510</v>
+        <v>170</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="14">
-        <v>3</v>
+        <v>507</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="I16" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>25</v>
       </c>
@@ -3591,51 +3672,57 @@
         <v>26</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>511</v>
+        <v>170</v>
       </c>
       <c r="E17" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="F17" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="F17" s="14">
-        <v>5</v>
       </c>
       <c r="G17" s="14">
         <v>3</v>
       </c>
       <c r="H17" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I17" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>26</v>
+        <v>517</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>32</v>
+        <v>262</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>512</v>
+        <v>170</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="14">
-        <v>3</v>
+        <v>518</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I18" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>25</v>
       </c>
@@ -3643,103 +3730,115 @@
         <v>26</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>513</v>
+        <v>170</v>
       </c>
       <c r="E19" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>6</v>
-      </c>
-      <c r="F19" s="14">
-        <v>4</v>
       </c>
       <c r="G19" s="14">
         <v>4</v>
       </c>
       <c r="H19" s="14">
+        <v>4</v>
+      </c>
+      <c r="I19" s="14">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>33</v>
+        <v>258</v>
       </c>
       <c r="B20" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>5</v>
+      </c>
+      <c r="I20" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>523</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="F21" s="14" t="s">
         <v>6</v>
-      </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
-      <c r="H20" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="14">
-        <v>4</v>
       </c>
       <c r="G21" s="14">
         <v>3</v>
       </c>
       <c r="H21" s="14">
+        <v>5</v>
+      </c>
+      <c r="I21" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>37</v>
-      </c>
       <c r="C22" s="14" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="14">
-        <v>3</v>
+        <v>502</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
         <v>4</v>
       </c>
-      <c r="H22" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>36</v>
       </c>
@@ -3750,126 +3849,141 @@
         <v>39</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="E23" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="14">
+      <c r="G23" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="14">
+      <c r="H23" s="14">
         <v>4</v>
       </c>
-      <c r="H23" s="14">
+      <c r="I23" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>517</v>
+        <v>26</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" s="14">
-        <v>2</v>
+        <v>509</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="G24" s="14">
         <v>5</v>
       </c>
       <c r="H24" s="14">
+        <v>3</v>
+      </c>
+      <c r="I24" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="14">
+        <v>2</v>
+      </c>
+      <c r="H25" s="14">
+        <v>5</v>
+      </c>
+      <c r="I25" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="14">
+    <row r="26" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="14">
         <v>4</v>
       </c>
-      <c r="G25" s="14">
+      <c r="H26" s="14">
+        <v>3</v>
+      </c>
+      <c r="I26" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="25">
+        <v>3</v>
+      </c>
+      <c r="H27" s="25">
         <v>4</v>
       </c>
-      <c r="H25" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="14">
-        <v>2</v>
-      </c>
-      <c r="G26" s="14">
-        <v>1</v>
-      </c>
-      <c r="H26" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="28" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>524</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>525</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="25">
-        <v>3</v>
-      </c>
-      <c r="G27" s="25">
-        <v>5</v>
-      </c>
-      <c r="H27" s="25">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -3878,8 +3992,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="26"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -3888,8 +4003,9 @@
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="24"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -3898,8 +4014,12 @@
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
     </row>
   </sheetData>
+  <sortState ref="A2:I27">
+    <sortCondition ref="C2:C27"/>
+  </sortState>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -3907,7 +4027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3943,19 +4063,19 @@
     </row>
     <row r="4" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="D4" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>272</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>274</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>55</v>
@@ -3963,19 +4083,19 @@
     </row>
     <row r="5" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="D5" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>277</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>55</v>
@@ -3983,7 +4103,7 @@
     </row>
     <row r="6" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>49</v>
@@ -3995,70 +4115,70 @@
         <v>51</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>51</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>282</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>282</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4075,7 +4195,7 @@
         <v>59</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>52</v>
@@ -4086,16 +4206,16 @@
         <v>51</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="E11" s="15" t="s">
         <v>288</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>290</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>58</v>
@@ -4106,7 +4226,7 @@
         <v>51</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>62</v>
@@ -4129,16 +4249,16 @@
         <v>60</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4149,16 +4269,16 @@
         <v>61</v>
       </c>
       <c r="C14" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>295</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4172,10 +4292,10 @@
         <v>66</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>67</v>
@@ -4183,10 +4303,10 @@
     </row>
     <row r="16" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>53</v>
@@ -4195,10 +4315,10 @@
         <v>54</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4211,30 +4331,30 @@
         <v>69</v>
       </c>
       <c r="B18" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="E18" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="F18" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="G18" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="H18" s="17" t="s">
         <v>306</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -4246,7 +4366,7 @@
     </row>
     <row r="20" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>70</v>
@@ -4272,33 +4392,33 @@
     </row>
     <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>313</v>
-      </c>
       <c r="E21" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>70</v>
@@ -4324,7 +4444,7 @@
     </row>
     <row r="23" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>55</v>
@@ -4350,7 +4470,7 @@
     </row>
     <row r="24" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>55</v>
@@ -4365,7 +4485,7 @@
         <v>55</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G24" s="19" t="s">
         <v>72</v>
@@ -4376,7 +4496,7 @@
     </row>
     <row r="25" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>55</v>
@@ -4402,7 +4522,7 @@
     </row>
     <row r="26" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -4414,7 +4534,7 @@
     </row>
     <row r="27" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>55</v>
@@ -4440,7 +4560,7 @@
     </row>
     <row r="28" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>75</v>
@@ -4466,7 +4586,7 @@
     </row>
     <row r="29" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>55</v>
@@ -4492,7 +4612,7 @@
     </row>
     <row r="30" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>55</v>
@@ -4518,7 +4638,7 @@
     </row>
     <row r="31" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>55</v>
@@ -4544,7 +4664,7 @@
     </row>
     <row r="32" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>55</v>
@@ -4845,7 +4965,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4870,7 +4990,7 @@
         <v>79</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4878,16 +4998,16 @@
         <v>81</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4895,16 +5015,16 @@
         <v>82</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4912,10 +5032,10 @@
         <v>83</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>6</v>
@@ -4932,7 +5052,7 @@
         <v>85</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>6</v>
@@ -4946,16 +5066,16 @@
         <v>86</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4963,16 +5083,16 @@
         <v>87</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4980,16 +5100,16 @@
         <v>88</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4997,7 +5117,7 @@
         <v>89</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>90</v>
@@ -5014,101 +5134,101 @@
         <v>91</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>348</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>350</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>485</v>
-      </c>
       <c r="C15" s="19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5116,10 +5236,10 @@
         <v>92</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>6</v>
@@ -5133,10 +5253,10 @@
         <v>93</v>
       </c>
       <c r="B17" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>356</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>358</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>6</v>
@@ -5150,10 +5270,10 @@
         <v>94</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>6</v>
@@ -5164,172 +5284,172 @@
     </row>
     <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>98</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -5339,7 +5459,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5352,10 +5472,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>102</v>
@@ -5378,16 +5498,16 @@
         <v>81</v>
       </c>
       <c r="C2" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>384</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="F2" s="22" t="s">
         <v>385</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5398,16 +5518,16 @@
         <v>82</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="E3" s="22" t="s">
         <v>388</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="F3" s="22" t="s">
         <v>389</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5418,16 +5538,16 @@
         <v>83</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>392</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="F4" s="22" t="s">
         <v>393</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>394</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5438,16 +5558,16 @@
         <v>84</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>396</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="F5" s="22" t="s">
         <v>397</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5458,16 +5578,16 @@
         <v>86</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>400</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="F6" s="22" t="s">
         <v>401</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>402</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5481,13 +5601,13 @@
         <v>112</v>
       </c>
       <c r="D7" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>404</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>405</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5498,16 +5618,16 @@
         <v>88</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>407</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="F8" s="22" t="s">
         <v>408</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>409</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -5518,16 +5638,16 @@
         <v>89</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="F9" s="22" t="s">
         <v>412</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -5538,116 +5658,116 @@
         <v>91</v>
       </c>
       <c r="C10" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="F10" s="22" t="s">
         <v>416</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>417</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="E11" s="22" t="s">
         <v>420</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="F11" s="22" t="s">
         <v>421</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>422</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="C12" s="19" t="s">
+      <c r="E12" s="22" t="s">
         <v>425</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="F12" s="23" t="s">
         <v>426</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>427</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="E13" s="22" t="s">
         <v>430</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="F13" s="22" t="s">
         <v>431</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>432</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="E14" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>435</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>487</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="E15" s="22" t="s">
+      <c r="F15" s="22" t="s">
         <v>489</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5658,16 +5778,16 @@
         <v>92</v>
       </c>
       <c r="C16" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="E16" s="22" t="s">
         <v>438</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="F16" s="22" t="s">
         <v>439</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>440</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -5678,16 +5798,16 @@
         <v>93</v>
       </c>
       <c r="C17" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="F17" s="22" t="s">
         <v>442</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5698,216 +5818,216 @@
         <v>94</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E18" s="22" t="s">
         <v>445</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="F18" s="22" t="s">
         <v>446</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>447</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>449</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>451</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="D20" s="19" t="s">
         <v>453</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>455</v>
       </c>
       <c r="E20" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="D21" s="19" t="s">
         <v>456</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>458</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="D22" s="19" t="s">
         <v>459</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>461</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>463</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>465</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="D24" s="19" t="s">
         <v>467</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>469</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="D25" s="19" t="s">
         <v>471</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>473</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="D26" s="19" t="s">
         <v>475</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>477</v>
       </c>
       <c r="E26" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="D27" s="19" t="s">
         <v>478</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>480</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>122</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -5917,13 +6037,13 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="41.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -6011,7 +6131,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -6392,7 +6512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6439,8 +6559,8 @@
       <c r="E2" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>152</v>
+      <c r="F2" s="27" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -6450,7 +6570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6462,16 +6582,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6479,13 +6599,13 @@
         <v>124</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -6496,10 +6616,10 @@
         <v>74</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6513,10 +6633,10 @@
         <v>125</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>74</v>
@@ -6527,13 +6647,13 @@
         <v>74</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -6541,13 +6661,13 @@
         <v>74</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -6555,13 +6675,13 @@
         <v>74</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -6569,13 +6689,13 @@
         <v>74</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -6583,13 +6703,13 @@
         <v>74</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>529</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6603,10 +6723,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>74</v>
@@ -6620,10 +6740,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -6634,10 +6754,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -6648,10 +6768,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6665,10 +6785,10 @@
         <v>76</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>74</v>
@@ -6679,13 +6799,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6693,13 +6813,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6707,13 +6827,13 @@
         <v>74</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6727,10 +6847,10 @@
         <v>100</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>74</v>
@@ -6741,13 +6861,13 @@
         <v>74</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -6755,13 +6875,13 @@
         <v>74</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -6769,13 +6889,13 @@
         <v>74</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -6789,13 +6909,13 @@
         <v>142</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -6806,25 +6926,25 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>214</v>
       </c>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D30" s="8"/>
     </row>
@@ -6836,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D31" s="8"/>
     </row>
@@ -6848,7 +6968,7 @@
         <v>80</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D32" s="8"/>
     </row>
@@ -6860,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D33" s="8"/>
     </row>
@@ -6872,7 +6992,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D34" s="8"/>
     </row>
@@ -6884,13 +7004,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D36" s="8"/>
     </row>
@@ -6902,7 +7022,7 @@
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D37" s="8"/>
     </row>
@@ -6914,7 +7034,7 @@
         <v>44</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D38" s="8"/>
     </row>
@@ -6926,7 +7046,7 @@
         <v>45</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D39" s="8"/>
     </row>
@@ -6938,7 +7058,7 @@
         <v>46</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D40" s="8"/>
     </row>
@@ -6950,7 +7070,7 @@
         <v>47</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D41" s="8"/>
     </row>
@@ -6959,10 +7079,10 @@
         <v>74</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D42" s="8"/>
     </row>
@@ -6971,10 +7091,10 @@
         <v>74</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D43" s="8"/>
     </row>
@@ -6983,10 +7103,10 @@
         <v>74</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D44" s="8"/>
     </row>
@@ -6998,13 +7118,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D46" s="8"/>
     </row>
@@ -7016,7 +7136,7 @@
         <v>77</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D47" s="8"/>
     </row>
@@ -7028,7 +7148,7 @@
         <v>78</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D48" s="8"/>
     </row>
@@ -7040,7 +7160,7 @@
         <v>79</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D49" s="8"/>
     </row>
@@ -7052,7 +7172,7 @@
         <v>80</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D50" s="8"/>
     </row>
@@ -7064,13 +7184,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D52" s="8"/>
     </row>
@@ -7082,7 +7202,7 @@
         <v>101</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D53" s="8"/>
     </row>
@@ -7094,7 +7214,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D54" s="8"/>
     </row>
@@ -7106,7 +7226,7 @@
         <v>103</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D55" s="8"/>
     </row>
@@ -7118,7 +7238,7 @@
         <v>104</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D56" s="8"/>
     </row>
@@ -7130,7 +7250,7 @@
         <v>105</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D57" s="8"/>
     </row>
@@ -7142,13 +7262,13 @@
     </row>
     <row r="59" spans="1:4" ht="28" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="D59" s="8"/>
     </row>
@@ -7160,7 +7280,7 @@
         <v>126</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D60" s="8"/>
     </row>
@@ -7172,13 +7292,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>142</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D62" s="8"/>
     </row>
@@ -7190,7 +7310,7 @@
         <v>143</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D63" s="8"/>
     </row>
@@ -7202,7 +7322,7 @@
         <v>144</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D64" s="8"/>
     </row>
@@ -7214,7 +7334,7 @@
         <v>145</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D65" s="8"/>
     </row>
@@ -7226,7 +7346,7 @@
         <v>146</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D66" s="8"/>
     </row>
@@ -7238,7 +7358,7 @@
         <v>147</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D67" s="8"/>
     </row>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEEBDC8-8028-4317-BEB4-63049FA46F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
@@ -21,22 +22,11 @@
     <sheet name="ID说明与列名解释" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="538">
   <si>
     <t>需求 ID</t>
   </si>
@@ -104,9 +94,6 @@
     <t>RSK-1.3.002</t>
   </si>
   <si>
-    <t>热数据不足时补齐冷数据失败，返回结果不完整</t>
-  </si>
-  <si>
     <t>RSK-1.5.001</t>
   </si>
   <si>
@@ -530,565 +517,1959 @@
     <t>1.1.xxx</t>
   </si>
   <si>
+    <t>RSK-1.1.001: HBase写入失败</t>
+  </si>
+  <si>
+    <t>1.2.xxx</t>
+  </si>
+  <si>
+    <t>RSK-1.2.001: 数据丢失风险</t>
+  </si>
+  <si>
+    <t>1.3.xxx</t>
+  </si>
+  <si>
+    <t>RSK-1.3.001: MIGRATING状态保护</t>
+  </si>
+  <si>
+    <t>1.4.xxx</t>
+  </si>
+  <si>
+    <t>RSK-1.4.001: 状态锁定</t>
+  </si>
+  <si>
+    <t>1.5.xxx</t>
+  </si>
+  <si>
+    <t>RSK-1.5.001: 补齐失败</t>
+  </si>
+  <si>
+    <t>P{数字}</t>
+  </si>
+  <si>
+    <t>风险优先级 = Tech Risk × Bus. Risk</t>
+  </si>
+  <si>
+    <t>最高优先级，必须覆盖</t>
+  </si>
+  <si>
+    <t>Risk Pri. &gt;= 12 或 Extensive测试</t>
+  </si>
+  <si>
+    <t>中等优先级，建议覆盖</t>
+  </si>
+  <si>
+    <t>Risk Pri. 6-9</t>
+  </si>
+  <si>
+    <t>低优先级，可选覆盖</t>
+  </si>
+  <si>
+    <t>Risk Pri. &lt;= 4 或 Cursory测试</t>
+  </si>
+  <si>
+    <t>TCI-{类型}-{序号}</t>
+  </si>
+  <si>
+    <t>Test Coverage Item(测试覆盖项)</t>
+  </si>
+  <si>
+    <t>TCI-STT-xx</t>
+  </si>
+  <si>
+    <t>基于状态转移表的覆盖项</t>
+  </si>
+  <si>
+    <t>TCI-STT-01: 标准迁移路径</t>
+  </si>
+  <si>
+    <t>TCI-DT-xx</t>
+  </si>
+  <si>
+    <t>基于决策表的覆盖项</t>
+  </si>
+  <si>
+    <t>TCI-DT-04: 幂等自愈</t>
+  </si>
+  <si>
+    <t>TCI-BVA-xx</t>
+  </si>
+  <si>
+    <t>基于边界值分析的覆盖项</t>
+  </si>
+  <si>
+    <t>TCI-BVA-04: 评论数2001</t>
+  </si>
+  <si>
+    <t>TC-{类型}-{序号}</t>
+  </si>
+  <si>
+    <t>Test Case(测试用例)</t>
+  </si>
+  <si>
+    <t>TC-STT-xx</t>
+  </si>
+  <si>
+    <t>状态转移表相关用例</t>
+  </si>
+  <si>
+    <t>TC-STT-01: 标准冷迁移</t>
+  </si>
+  <si>
+    <t>TC-DT-xx</t>
+  </si>
+  <si>
+    <t>决策表相关用例</t>
+  </si>
+  <si>
+    <t>TC-DT-04: 幂等自愈测试</t>
+  </si>
+  <si>
+    <t>TC-BVA-xx</t>
+  </si>
+  <si>
+    <t>边界值相关用例</t>
+  </si>
+  <si>
+    <t>TC-BVA-04: 评论数边界</t>
+  </si>
+  <si>
+    <t>BUG-{模块}-{序号}</t>
+  </si>
+  <si>
+    <t>Bug Report(缺陷报告)</t>
+  </si>
+  <si>
+    <t>BUG-COLD-001: 状态机自愈逻辑缺陷</t>
+  </si>
+  <si>
+    <t>Sheet名称</t>
+  </si>
+  <si>
+    <t>列名</t>
+  </si>
+  <si>
+    <t>列名解释</t>
+  </si>
+  <si>
+    <t>需求与风险</t>
+  </si>
+  <si>
+    <t>功能需求的唯一标识符，格式为REQ-M{数字}</t>
+  </si>
+  <si>
+    <t>对该功能的简要描述</t>
+  </si>
+  <si>
+    <t>与该需求相关的质量风险编号</t>
+  </si>
+  <si>
+    <t>风险的具体描述，说明可能产生的问题</t>
+  </si>
+  <si>
+    <t>风险的优先级，P0最高，P2最低</t>
+  </si>
+  <si>
+    <t>逻辑模型</t>
+  </si>
+  <si>
+    <t>状态转移表中的起始状态</t>
+  </si>
+  <si>
+    <t>触发状态转移的事件</t>
+  </si>
+  <si>
+    <t>状态转移的前置条件</t>
+  </si>
+  <si>
+    <t>状态转移后的目标状态</t>
+  </si>
+  <si>
+    <t>状态转移时执行的操作</t>
+  </si>
+  <si>
+    <t>对应需求文档中的用例编号(M-1至M-7)</t>
+  </si>
+  <si>
+    <t>C1-C5</t>
+  </si>
+  <si>
+    <t>决策表中的条件(Condition)</t>
+  </si>
+  <si>
+    <t>R1-R7</t>
+  </si>
+  <si>
+    <t>决策表中的规则(Rule)</t>
+  </si>
+  <si>
+    <t>A1-A5</t>
+  </si>
+  <si>
+    <t>决策表中的动作(Action)</t>
+  </si>
+  <si>
+    <t>覆盖项清单</t>
+  </si>
+  <si>
+    <t>测试覆盖项的唯一标识</t>
+  </si>
+  <si>
+    <t>该覆盖项所属的测试模块</t>
+  </si>
+  <si>
+    <t>该覆盖项需要验证的具体逻辑</t>
+  </si>
+  <si>
+    <t>覆盖项的执行优先级(P0/P1/P2)</t>
+  </si>
+  <si>
+    <t>该覆盖项对应的风险编号</t>
+  </si>
+  <si>
+    <t>测试用例</t>
+  </si>
+  <si>
+    <t>测试用例的唯一标识</t>
+  </si>
+  <si>
+    <t>该用例对应的测试覆盖项</t>
+  </si>
+  <si>
+    <t>用例的测试场景描述</t>
+  </si>
+  <si>
+    <t>执行测试前需要满足的条件</t>
+  </si>
+  <si>
+    <t>具体的测试操作步骤</t>
+  </si>
+  <si>
+    <t>测试执行后的预期输出</t>
+  </si>
+  <si>
+    <t>追溯矩阵</t>
+  </si>
+  <si>
+    <t>需求ID→风险ID→TCI→用例</t>
+  </si>
+  <si>
+    <t>从需求到测试用例的完整追溯链</t>
+  </si>
+  <si>
+    <t>对应的JUnit测试方法名称</t>
+  </si>
+  <si>
+    <t>缺陷报告</t>
+  </si>
+  <si>
+    <t>缺陷的唯一标识</t>
+  </si>
+  <si>
+    <t>发现该缺陷的测试用例</t>
+  </si>
+  <si>
+    <t>缺陷的详细描述</t>
+  </si>
+  <si>
+    <t>修复前的测试失败信息</t>
+  </si>
+  <si>
+    <t>修复后的测试通过信息</t>
+  </si>
+  <si>
+    <t>缺陷修复验证的结果</t>
+  </si>
+  <si>
+    <t>REQ-M1-S</t>
+  </si>
+  <si>
+    <t>RSK-1.1.005</t>
+  </si>
+  <si>
+    <t>REQ-M3-C</t>
+  </si>
+  <si>
+    <t>REQ-M8</t>
+  </si>
+  <si>
+    <t>REQ-M9</t>
+  </si>
+  <si>
+    <t>COLD 状态删除后，HBase 归档未清理造成存储浪费</t>
+  </si>
+  <si>
+    <t>REQ-M10</t>
+  </si>
+  <si>
+    <t>NONE (PENDING)</t>
+  </si>
+  <si>
+    <t>管理员审核通过</t>
+  </si>
+  <si>
+    <t>migration_status == 'NONE'</t>
+  </si>
+  <si>
+    <t>NONE (APPROVED)</t>
+  </si>
+  <si>
+    <t>设置公开可见</t>
+  </si>
+  <si>
+    <t>管理员审核拒绝</t>
+  </si>
+  <si>
+    <t>NONE (REJECTED)</t>
+  </si>
+  <si>
+    <t>仅作者可见</t>
+  </si>
+  <si>
+    <t>原子更新 migration_status</t>
+  </si>
+  <si>
+    <t>M-1/M-1S</t>
+  </si>
+  <si>
+    <t>last_access &gt; 3d</t>
+  </si>
+  <si>
+    <t>M-1/M1-S</t>
+  </si>
+  <si>
+    <t>用户修改内容</t>
+  </si>
+  <si>
+    <t>重置审核状态，隐藏动态</t>
+  </si>
+  <si>
+    <t>M-10</t>
+  </si>
+  <si>
+    <t>重置审核状态</t>
+  </si>
+  <si>
+    <t>提交事务，MySQL 记录消失</t>
+  </si>
+  <si>
+    <t>迁移执行 (成功)</t>
+  </si>
+  <si>
+    <t>HBase 写入/校验失败</t>
+  </si>
+  <si>
+    <t>NONE (保持原审核状态)</t>
+  </si>
+  <si>
+    <t>记录日志，回滚 migration_status</t>
+  </si>
+  <si>
+    <t>迁移执行 (异常)</t>
+  </si>
+  <si>
+    <t>评论/点赞/修改内容/修改审核状态</t>
+  </si>
+  <si>
+    <t>拒绝请求 (抛出异常)</t>
+  </si>
+  <si>
+    <t>M-5/M-8</t>
+  </si>
+  <si>
+    <t>用户触发 RESTORE 事件</t>
+  </si>
+  <si>
+    <t>发送 MQ，写回后删 HBase</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>补齐数据并异步恢复</t>
+  </si>
+  <si>
+    <t>ANY</t>
+  </si>
+  <si>
+    <t>物理删除 MySQL 记录，清理 HBase</t>
+  </si>
+  <si>
+    <t>M-9</t>
+  </si>
+  <si>
+    <t>R1 (热数据)</t>
+  </si>
+  <si>
+    <t>R2 (内容修改)</t>
+  </si>
+  <si>
+    <t>R3 (审核中)</t>
+  </si>
+  <si>
+    <t>R4 (热点拦截)</t>
+  </si>
+  <si>
+    <t>R5 (迁移成功)</t>
+  </si>
+  <si>
+    <t>R6 (写入失败)</t>
+  </si>
+  <si>
+    <t>R7 (幂等自愈)</t>
+  </si>
+  <si>
+    <t>条件 (Conditions)</t>
+  </si>
+  <si>
+    <t>C1: 是否满足冷时间阈值</t>
+  </si>
+  <si>
+    <t>C2: 当前审核状态</t>
+  </si>
+  <si>
+    <t>APP/REJ</t>
+  </si>
+  <si>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>C3: 用户执行修改内容</t>
+  </si>
+  <si>
+    <t>C4: 评论数 ≤ 2000</t>
+  </si>
+  <si>
+    <t>C5: HBase 存储结果</t>
+  </si>
+  <si>
+    <t>成功/已有</t>
+  </si>
+  <si>
+    <t>C6: MySQL 删除结果</t>
+  </si>
+  <si>
+    <t>动作 (Actions)</t>
+  </si>
+  <si>
+    <t>A1: 获取/保持锁定</t>
+  </si>
+  <si>
+    <t>A2: 跳过迁移</t>
+  </si>
+  <si>
+    <t>A3: 审核状态回滚至 PENDING</t>
+  </si>
+  <si>
+    <t>A4: 迁移状态恢复 (NONE)</t>
+  </si>
+  <si>
+    <t>A5: 删除 MySQL 记录</t>
+  </si>
+  <si>
+    <t>A6: 迁移完成 (进入 COLD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关联风险 ID </t>
+  </si>
+  <si>
+    <t>迁移流程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">标准路径：验证从 APPROVED 和 REJECTED 经 MIGRATING 到 COLD 的完整迁移路径 </t>
+  </si>
+  <si>
+    <t>RSK-1.1.001 / 1.2.002</t>
+  </si>
+  <si>
+    <t>迁移逻辑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阈值拦截：验证评论数 &gt; 2000 时，从 MIGRATING 回滚至原状态 </t>
+  </si>
+  <si>
+    <t>RSK-1.1.004 / 1.4.001</t>
+  </si>
+  <si>
+    <t>事务异常</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写入失败回滚：验证 HBase 写入/校验失败时，事务回滚并恢复原状态 </t>
+  </si>
+  <si>
+    <t>自愈机制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幂等自愈：验证迁移中断（如 MySQL 未删但 HBase 已有）后的断点续传逻辑 </t>
+  </si>
+  <si>
+    <t>RSK-1.1.003 / 1.4.002</t>
+  </si>
+  <si>
+    <t>恢复流程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主动激活：验证从 COLD 状态通过 RESTORE 事件写回 MySQL 并删除 HBase 记录 </t>
+  </si>
+  <si>
+    <t>RSK-1.2.003 / 1.3.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">隐式触发：验证列表查询热数据不足时，触发冷数据补齐及异步恢复 </t>
+  </si>
+  <si>
+    <t>审核逻辑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">审核流转：验证 PENDING 状态经管理员审核转向 APPROVED 或 REJECTED </t>
+  </si>
+  <si>
+    <t>TCI-STT-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内容修改回滚：验证已审核动态（APPROVED/REJECTED）修改后一律回滚至 PENDING </t>
+  </si>
+  <si>
+    <t>TCI-STT-11</t>
+  </si>
+  <si>
+    <t>生命周期</t>
+  </si>
+  <si>
+    <t xml:space="preserve">多阶段删除：验证 ACTIVE、MIGRATING、COLD 各阶段下的物理删除及归档清理 </t>
+  </si>
+  <si>
+    <t>TCI-STT-12</t>
+  </si>
+  <si>
+    <t>验证动态从冷数据迁回sql后，迁移状态修改为NONE，审核状态保持不变</t>
+  </si>
+  <si>
+    <t>TCI-STT-13</t>
+  </si>
+  <si>
+    <t>验证审核状态为PENDING的动态不会进行迁移</t>
+  </si>
+  <si>
+    <t>决策逻辑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证 HBase 写入异常触发的完整事务回滚 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证 HBase 虚假成功（Put 成功但校验失败）的拦截逻辑 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">验证 MySQL 删除阶段超时导致的 MIGRATING 状态遗留场景 </t>
+  </si>
+  <si>
+    <t>TCI-BVA-01-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">评论数临界点：0 条（空数据正常迁移验证） </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSK-1.4.002 / 1.1.004  </t>
+  </si>
+  <si>
+    <t>TCI-BVA-01-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">评论数临界点：1999 条（接近阈值的正常迁移） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-01-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">评论数临界点：2000 条（迁移阈值上限验证） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-01-D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">评论数临界点：2001 条（触发拦截拦截验证） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-02-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REJECTED 状态时间边界：71h（热数据状态，不迁移） </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSK-1.1.005  </t>
+  </si>
+  <si>
+    <t>TCI-BVA-02-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REJECTED 状态时间边界：72h（临界点，执行迁移） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-02-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REJECTED 状态时间边界：73h（冷数据状态，执行迁移） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-03-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPROVED 状态时间边界：167h（热数据状态，不迁移） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-03-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPROVED 状态时间边界：168h（临界点，执行迁移） </t>
+  </si>
+  <si>
+    <t>TCI-BVA-03-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APPROVED 状态时间边界：169h（冷数据状态，执行迁移） </t>
+  </si>
+  <si>
+    <t>用例 ID</t>
+  </si>
+  <si>
+    <t>关联 TCI ID</t>
+  </si>
+  <si>
+    <t>标准冷迁移路径</t>
+  </si>
+  <si>
+    <t>动态状态为 APPROVED/REJECTED，评论数 &lt; 2000，满足时间阈值</t>
+  </si>
+  <si>
+    <r>
+      <t>触发定时迁移任务，检查数据库及</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>状态经历</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE-&gt;MIGRATING-&gt;DELETED(COLD)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录消失，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>存在归档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>评论数超限拦截</t>
+  </si>
+  <si>
+    <t>动态状态为 NONE，满足时间阈值，但评论数 = 2001</t>
+  </si>
+  <si>
+    <t>触发定时迁移任务</t>
+  </si>
+  <si>
+    <r>
+      <t>状态瞬时变为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MIGRATING </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后回滚为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录保留，不写入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HBase </t>
+    </r>
+  </si>
+  <si>
+    <t>写入失败回滚</t>
+  </si>
+  <si>
+    <t>动态符合迁移条件</t>
+  </si>
+  <si>
+    <r>
+      <t>触发任务，模拟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>连接超时或写入失败</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>事务回滚，状态恢复为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE </t>
+    </r>
+  </si>
+  <si>
+    <t>MIGRATING 状态保护</t>
+  </si>
+  <si>
+    <t>动态处于 MIGRATING 状态</t>
+  </si>
+  <si>
+    <t>用户尝试评论、点赞或修改该动态</t>
+  </si>
+  <si>
+    <r>
+      <t>系统抛出业务异常，拒绝请求，数据库无数据变更</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>幂等自愈(断点续传)</t>
+  </si>
+  <si>
+    <t>状态为 MIGRATING，HBase 已有数据但 MySQL 未删</t>
+  </si>
+  <si>
+    <t>再次触发定时任务</t>
+  </si>
+  <si>
+    <r>
+      <t>检测到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已有数据，跳过写入直接删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MySQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，进入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> COLD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>动态处于 COLD 状态</t>
+  </si>
+  <si>
+    <r>
+      <t>用户在前端点击激活</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>恢复</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>发送</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> RESTORE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>插入数据（状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>列表查询隐式恢复</t>
+  </si>
+  <si>
+    <t>热数据页不足，COLD 库中有数据</t>
+  </si>
+  <si>
+    <t>用户访问动态列表页</t>
+  </si>
+  <si>
+    <r>
+      <t>返回热</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冷混合数据，后台异步触发冷数据恢复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>访问时间更新</t>
+  </si>
+  <si>
+    <t>状态为 NONE，last_access 为 6d 前</t>
+  </si>
+  <si>
+    <t>用户查看动态详情</t>
+  </si>
+  <si>
+    <r>
+      <t>状态保持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">last_access_time </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新为当前时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>审核流转路径</t>
+  </si>
+  <si>
+    <t>动态为 PENDING 状态</t>
+  </si>
+  <si>
+    <t>管理员分别执行审核通过和拒绝操作</t>
+  </si>
+  <si>
+    <r>
+      <t>状态分别流向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE(APPROVED) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE(REJECTED) </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-STT-10</t>
+  </si>
+  <si>
+    <t>修改内容状态重置</t>
+  </si>
+  <si>
+    <t>状态为 APPROVED/REJECTED</t>
+  </si>
+  <si>
+    <t>用户修改动态内容</t>
+  </si>
+  <si>
+    <r>
+      <t>无论原状态为何，一律变回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> PENDING </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态并隐藏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-STT-11</t>
+  </si>
+  <si>
+    <t>生命周期物理删除</t>
+  </si>
+  <si>
+    <t>动态处于任意阶段（ACTIVE/COLD等）</t>
+  </si>
+  <si>
+    <t>用户执行删除操作</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录删除，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>归档同步清理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-STT-12</t>
+  </si>
+  <si>
+    <t>恢复后状态保持</t>
+  </si>
+  <si>
+    <t>动态从 COLD 恢复</t>
+  </si>
+  <si>
+    <t>执行恢复流程</t>
+  </si>
+  <si>
+    <r>
+      <t>迁移状态变回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，原审核状态（如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> REJECTED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）保持不变</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-STT-13</t>
+  </si>
+  <si>
+    <t>审核中拦截</t>
+  </si>
+  <si>
+    <t>动态状态为 PENDING</t>
+  </si>
+  <si>
+    <r>
+      <t>即使满足时间条件，也不进入迁移流程</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>HBase 写入异常回滚</t>
+  </si>
+  <si>
+    <t>符合 Rule 6 场景</t>
+  </si>
+  <si>
+    <r>
+      <t>手动关闭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HBase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>服务后执行迁移</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>事务感知异常并回滚，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>状态回滚为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> NONE </t>
+    </r>
+  </si>
+  <si>
+    <t>虚假成功校验</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>环境下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Put </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成功但</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> exists </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>校验返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> false</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>触发校验失败异常，事务回滚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>MySQL 删除超时</t>
+  </si>
+  <si>
+    <t>符合 Rule 7 场景</t>
+  </si>
+  <si>
+    <t>对目标行加锁模拟死锁或超时</t>
+  </si>
+  <si>
+    <r>
+      <t>状态保持为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MIGRATING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，等待下次重试</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-BVA-01-A</t>
+  </si>
+  <si>
+    <t>评论数下限(0)</t>
+  </si>
+  <si>
+    <t>评论数 = 0</t>
+  </si>
+  <si>
+    <r>
+      <t>正常迁移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-BVA-01-B</t>
+  </si>
+  <si>
+    <t>评论数临界(1999)</t>
+  </si>
+  <si>
+    <t>评论数 = 1999</t>
+  </si>
+  <si>
+    <t>TC-BVA-01-C</t>
+  </si>
+  <si>
+    <t>评论数阈值(2000)</t>
+  </si>
+  <si>
+    <t>评论数 = 2000</t>
+  </si>
+  <si>
+    <t>TC-BVA-01-D</t>
+  </si>
+  <si>
+    <t>评论数超限(2001)</t>
+  </si>
+  <si>
+    <t>评论数 = 2001</t>
+  </si>
+  <si>
+    <r>
+      <t>触发拦截，状态回滚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-BVA-02-A</t>
+  </si>
+  <si>
+    <t>REJ 状态时间(71h)</t>
+  </si>
+  <si>
+    <t>REJECTED 状态满 71h</t>
+  </si>
+  <si>
+    <r>
+      <t>热数据状态，跳过迁移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-BVA-02-B</t>
+  </si>
+  <si>
+    <t>REJ 状态时间(72h)</t>
+  </si>
+  <si>
+    <t>REJECTED 状态满 72h</t>
+  </si>
+  <si>
+    <r>
+      <t>达到阈值，开始迁移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-BVA-02-C</t>
+  </si>
+  <si>
+    <t>REJ 状态时间(73h)</t>
+  </si>
+  <si>
+    <t>REJECTED 状态满 73h</t>
+  </si>
+  <si>
+    <r>
+      <t>超过阈值，开始迁移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>TC-BVA-03-A</t>
+  </si>
+  <si>
+    <t>APP 状态时间(167h)</t>
+  </si>
+  <si>
+    <t>APPROVED 状态满 167h</t>
+  </si>
+  <si>
+    <t>TC-BVA-03-B</t>
+  </si>
+  <si>
+    <t>APP 状态时间(168h)</t>
+  </si>
+  <si>
+    <t>APPROVED 状态满 168h</t>
+  </si>
+  <si>
+    <t>APP 状态时间(169h)</t>
+  </si>
+  <si>
+    <t>APPROVED 状态满 169h</t>
+  </si>
+  <si>
+    <t>TCI-STT-14</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>审核逻辑</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有 APPROVED (已通过) 状态的内容才对他人可见</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC-STT-14</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>审核中不可见</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用用户接口获取所有动态</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>动态状态为 PENDING</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态为 PENDING的动态不可见</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风险 ID</t>
+  </si>
+  <si>
+    <t>Tech Risk</t>
+  </si>
+  <si>
+    <t>Bus. Risk</t>
+  </si>
+  <si>
+    <t>Risk Pri. #</t>
+  </si>
+  <si>
+    <t>迁移单个老动态到 HBase</t>
+  </si>
+  <si>
+    <t>HBase 写入失败或验证失败导致迁移中断</t>
+  </si>
+  <si>
+    <t>HBase 写入成功但 MySQL 删除失败，导致冷热数据重复</t>
+  </si>
+  <si>
+    <t>冷迁移时 HBase 写入失败，同时 MySQL 错误删除所有数据</t>
+  </si>
+  <si>
+    <t>HBase 未写入评论/点赞数据，MySQL 已删除导致数据丢失</t>
+  </si>
+  <si>
+    <t>动态按审核状态分阶梯迁移</t>
+  </si>
+  <si>
+    <t>状态判断逻辑错误，导致 PENDING 动态误迁移或时间错误</t>
+  </si>
+  <si>
+    <t>超过评论阈值未恢复 NONE，无法再次进入迁移流程</t>
+  </si>
+  <si>
+    <t>超过阈值恢复至 NONE 操作失败，帖子被锁定 24 小时</t>
+  </si>
+  <si>
+    <t>未通过审核内容被他人通过接口或列表查询获取</t>
+  </si>
+  <si>
+    <t>恢复时 HBase 读取失败，冷数据无法完整恢复</t>
+  </si>
+  <si>
+    <t>恢复时 MySQL 插入成功但评论/点赞插入失败</t>
+  </si>
+  <si>
+    <t>恢复过程中 HBase 读取异常，动态恢复但相关数据丢失</t>
+  </si>
+  <si>
+    <t>恢复后状态未正确设为 NONE，导致动态仍隐形</t>
+  </si>
+  <si>
+    <t>用户查询触发恢复与定时任务重试并发冲突</t>
+  </si>
+  <si>
+    <t>用户点击激活时 MQ 恢复事件发送或处理失败</t>
+  </si>
+  <si>
+    <t>恢复过程中审核状态变更，导致状态机冲突</t>
+  </si>
+  <si>
+    <t>MIGRATING 动态仍被允许加载/评论/点赞/修改</t>
+  </si>
+  <si>
+    <t>状态遗留后未重试，数据在冷热库间“失踪”</t>
+  </si>
+  <si>
+    <t>定时任务执行失败，遗留数据无法自动重试</t>
+  </si>
+  <si>
+    <t>访问冷动态查询回源</t>
+  </si>
+  <si>
+    <t>HBase 宕机时冷动态查询请求直接失败</t>
+  </si>
+  <si>
+    <t>NONE 状态才允许更新审核</t>
+  </si>
+  <si>
+    <t>迁移中状态被修改，导致数据不一致或逻辑违例</t>
+  </si>
+  <si>
+    <t>彻底删除动态</t>
+  </si>
+  <si>
+    <t>用户删除</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>迁移中拒绝点赞/评论/修改操作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户修改动态内容</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改后审核状态未及时回退，违规内容绕过审核公开</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅通过审核的内容对他人可见</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风险类别</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>Data Consistency(数据一致性)</t>
-  </si>
-  <si>
-    <t>RSK-1.1.001: HBase写入失败</t>
-  </si>
-  <si>
-    <t>1.2.xxx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Data Integrity(数据完整性)</t>
-  </si>
-  <si>
-    <t>RSK-1.2.001: 数据丢失风险</t>
-  </si>
-  <si>
-    <t>1.3.xxx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>System Stability(系统稳定性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Functionality &amp; Availability(功能可用性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Concurrency Control(并发控制)</t>
-  </si>
-  <si>
-    <t>RSK-1.3.001: MIGRATING状态保护</t>
-  </si>
-  <si>
-    <t>1.4.xxx</t>
-  </si>
-  <si>
-    <t>RSK-1.4.001: 状态锁定</t>
-  </si>
-  <si>
-    <t>1.5.xxx</t>
-  </si>
-  <si>
-    <t>Functionality &amp; Availability(功能可用性)</t>
-  </si>
-  <si>
-    <t>RSK-1.5.001: 补齐失败</t>
-  </si>
-  <si>
-    <t>P{数字}</t>
-  </si>
-  <si>
-    <t>风险优先级 = Tech Risk × Bus. Risk</t>
-  </si>
-  <si>
-    <t>最高优先级，必须覆盖</t>
-  </si>
-  <si>
-    <t>Risk Pri. &gt;= 12 或 Extensive测试</t>
-  </si>
-  <si>
-    <t>中等优先级，建议覆盖</t>
-  </si>
-  <si>
-    <t>Risk Pri. 6-9</t>
-  </si>
-  <si>
-    <t>低优先级，可选覆盖</t>
-  </si>
-  <si>
-    <t>Risk Pri. &lt;= 4 或 Cursory测试</t>
-  </si>
-  <si>
-    <t>TCI-{类型}-{序号}</t>
-  </si>
-  <si>
-    <t>Test Coverage Item(测试覆盖项)</t>
-  </si>
-  <si>
-    <t>TCI-STT-xx</t>
-  </si>
-  <si>
-    <t>基于状态转移表的覆盖项</t>
-  </si>
-  <si>
-    <t>TCI-STT-01: 标准迁移路径</t>
-  </si>
-  <si>
-    <t>TCI-DT-xx</t>
-  </si>
-  <si>
-    <t>基于决策表的覆盖项</t>
-  </si>
-  <si>
-    <t>TCI-DT-04: 幂等自愈</t>
-  </si>
-  <si>
-    <t>TCI-BVA-xx</t>
-  </si>
-  <si>
-    <t>基于边界值分析的覆盖项</t>
-  </si>
-  <si>
-    <t>TCI-BVA-04: 评论数2001</t>
-  </si>
-  <si>
-    <t>TC-{类型}-{序号}</t>
-  </si>
-  <si>
-    <t>Test Case(测试用例)</t>
-  </si>
-  <si>
-    <t>TC-STT-xx</t>
-  </si>
-  <si>
-    <t>状态转移表相关用例</t>
-  </si>
-  <si>
-    <t>TC-STT-01: 标准冷迁移</t>
-  </si>
-  <si>
-    <t>TC-DT-xx</t>
-  </si>
-  <si>
-    <t>决策表相关用例</t>
-  </si>
-  <si>
-    <t>TC-DT-04: 幂等自愈测试</t>
-  </si>
-  <si>
-    <t>TC-BVA-xx</t>
-  </si>
-  <si>
-    <t>边界值相关用例</t>
-  </si>
-  <si>
-    <t>TC-BVA-04: 评论数边界</t>
-  </si>
-  <si>
-    <t>BUG-{模块}-{序号}</t>
-  </si>
-  <si>
-    <t>Bug Report(缺陷报告)</t>
-  </si>
-  <si>
-    <t>BUG-COLD-001: 状态机自愈逻辑缺陷</t>
-  </si>
-  <si>
-    <t>Sheet名称</t>
-  </si>
-  <si>
-    <t>列名</t>
-  </si>
-  <si>
-    <t>列名解释</t>
-  </si>
-  <si>
-    <t>需求与风险</t>
-  </si>
-  <si>
-    <t>功能需求的唯一标识符，格式为REQ-M{数字}</t>
-  </si>
-  <si>
-    <t>对该功能的简要描述</t>
-  </si>
-  <si>
-    <t>与该需求相关的质量风险编号</t>
-  </si>
-  <si>
-    <t>风险的具体描述，说明可能产生的问题</t>
-  </si>
-  <si>
-    <t>风险的优先级，P0最高，P2最低</t>
-  </si>
-  <si>
-    <t>逻辑模型</t>
-  </si>
-  <si>
-    <t>状态转移表中的起始状态</t>
-  </si>
-  <si>
-    <t>触发状态转移的事件</t>
-  </si>
-  <si>
-    <t>状态转移的前置条件</t>
-  </si>
-  <si>
-    <t>状态转移后的目标状态</t>
-  </si>
-  <si>
-    <t>状态转移时执行的操作</t>
-  </si>
-  <si>
-    <t>对应需求文档中的用例编号(M-1至M-7)</t>
-  </si>
-  <si>
-    <t>C1-C5</t>
-  </si>
-  <si>
-    <t>决策表中的条件(Condition)</t>
-  </si>
-  <si>
-    <t>R1-R7</t>
-  </si>
-  <si>
-    <t>决策表中的规则(Rule)</t>
-  </si>
-  <si>
-    <t>A1-A5</t>
-  </si>
-  <si>
-    <t>决策表中的动作(Action)</t>
-  </si>
-  <si>
-    <t>覆盖项清单</t>
-  </si>
-  <si>
-    <t>测试覆盖项的唯一标识</t>
-  </si>
-  <si>
-    <t>该覆盖项所属的测试模块</t>
-  </si>
-  <si>
-    <t>该覆盖项需要验证的具体逻辑</t>
-  </si>
-  <si>
-    <t>覆盖项的执行优先级(P0/P1/P2)</t>
-  </si>
-  <si>
-    <t>该覆盖项对应的风险编号</t>
-  </si>
-  <si>
-    <t>测试用例</t>
-  </si>
-  <si>
-    <t>测试用例的唯一标识</t>
-  </si>
-  <si>
-    <t>该用例对应的测试覆盖项</t>
-  </si>
-  <si>
-    <t>用例的测试场景描述</t>
-  </si>
-  <si>
-    <t>执行测试前需要满足的条件</t>
-  </si>
-  <si>
-    <t>具体的测试操作步骤</t>
-  </si>
-  <si>
-    <t>测试执行后的预期输出</t>
-  </si>
-  <si>
-    <t>追溯矩阵</t>
-  </si>
-  <si>
-    <t>需求ID→风险ID→TCI→用例</t>
-  </si>
-  <si>
-    <t>从需求到测试用例的完整追溯链</t>
-  </si>
-  <si>
-    <t>对应的JUnit测试方法名称</t>
-  </si>
-  <si>
-    <t>缺陷报告</t>
-  </si>
-  <si>
-    <t>缺陷的唯一标识</t>
-  </si>
-  <si>
-    <t>发现该缺陷的测试用例</t>
-  </si>
-  <si>
-    <t>缺陷的详细描述</t>
-  </si>
-  <si>
-    <t>修复前的测试失败信息</t>
-  </si>
-  <si>
-    <t>修复后的测试通过信息</t>
-  </si>
-  <si>
-    <t>缺陷修复验证的结果</t>
-  </si>
-  <si>
-    <t>REQ-M1-S</t>
-  </si>
-  <si>
-    <t>RSK-1.1.005</t>
-  </si>
-  <si>
-    <t>REQ-M3-C</t>
-  </si>
-  <si>
-    <t>RSK-1.3.010</t>
-  </si>
-  <si>
-    <t>RSK-1.3.009</t>
-  </si>
-  <si>
-    <t>REQ-M8</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>已修复，所有核心单元测试全部通过</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.1.006</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.1.007</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.2.006</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.3.002</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RSK-1.3.008</t>
-  </si>
-  <si>
-    <t>REQ-M9</t>
-  </si>
-  <si>
-    <t>RSK-1.2.005</t>
-  </si>
-  <si>
-    <t>COLD 状态删除后，HBase 归档未清理造成存储浪费</t>
-  </si>
-  <si>
-    <t>REQ-M10</t>
-  </si>
-  <si>
-    <t>RSK-1.3.011</t>
-  </si>
-  <si>
-    <t>NONE (PENDING)</t>
-  </si>
-  <si>
-    <t>管理员审核通过</t>
-  </si>
-  <si>
-    <t>migration_status == 'NONE'</t>
-  </si>
-  <si>
-    <t>NONE (APPROVED)</t>
-  </si>
-  <si>
-    <t>设置公开可见</t>
-  </si>
-  <si>
-    <t>管理员审核拒绝</t>
-  </si>
-  <si>
-    <t>NONE (REJECTED)</t>
-  </si>
-  <si>
-    <t>仅作者可见</t>
-  </si>
-  <si>
-    <t>原子更新 migration_status</t>
-  </si>
-  <si>
-    <t>M-1/M-1S</t>
-  </si>
-  <si>
-    <t>last_access &gt; 3d</t>
-  </si>
-  <si>
-    <t>M-1/M1-S</t>
-  </si>
-  <si>
-    <t>用户修改内容</t>
-  </si>
-  <si>
-    <t>重置审核状态，隐藏动态</t>
-  </si>
-  <si>
-    <t>M-10</t>
-  </si>
-  <si>
-    <t>重置审核状态</t>
-  </si>
-  <si>
-    <t>提交事务，MySQL 记录消失</t>
-  </si>
-  <si>
-    <t>迁移执行 (成功)</t>
-  </si>
-  <si>
-    <t>HBase 写入/校验失败</t>
-  </si>
-  <si>
-    <t>NONE (保持原审核状态)</t>
-  </si>
-  <si>
-    <t>记录日志，回滚 migration_status</t>
-  </si>
-  <si>
-    <t>迁移执行 (异常)</t>
-  </si>
-  <si>
-    <t>评论/点赞/修改内容/修改审核状态</t>
-  </si>
-  <si>
-    <t>拒绝请求 (抛出异常)</t>
-  </si>
-  <si>
-    <t>M-5/M-8</t>
-  </si>
-  <si>
-    <t>用户触发 RESTORE 事件</t>
-  </si>
-  <si>
-    <t>发送 MQ，写回后删 HBase</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>补齐数据并异步恢复</t>
-  </si>
-  <si>
-    <t>ANY</t>
-  </si>
-  <si>
-    <t>物理删除 MySQL 记录，清理 HBase</t>
-  </si>
-  <si>
-    <t>M-9</t>
-  </si>
-  <si>
-    <t>R1 (热数据)</t>
-  </si>
-  <si>
-    <t>R2 (内容修改)</t>
-  </si>
-  <si>
-    <t>R3 (审核中)</t>
-  </si>
-  <si>
-    <t>R4 (热点拦截)</t>
-  </si>
-  <si>
-    <t>R5 (迁移成功)</t>
-  </si>
-  <si>
-    <t>R6 (写入失败)</t>
-  </si>
-  <si>
-    <t>R7 (幂等自愈)</t>
-  </si>
-  <si>
-    <t>条件 (Conditions)</t>
-  </si>
-  <si>
-    <t>C1: 是否满足冷时间阈值</t>
-  </si>
-  <si>
-    <t>C2: 当前审核状态</t>
-  </si>
-  <si>
-    <t>APP/REJ</t>
-  </si>
-  <si>
-    <t>PENDING</t>
-  </si>
-  <si>
-    <t>C3: 用户执行修改内容</t>
-  </si>
-  <si>
-    <t>C4: 评论数 ≤ 2000</t>
-  </si>
-  <si>
-    <t>C5: HBase 存储结果</t>
-  </si>
-  <si>
-    <t>成功/已有</t>
-  </si>
-  <si>
-    <t>C6: MySQL 删除结果</t>
-  </si>
-  <si>
-    <t>动作 (Actions)</t>
-  </si>
-  <si>
-    <t>A1: 获取/保持锁定</t>
-  </si>
-  <si>
-    <t>A2: 跳过迁移</t>
-  </si>
-  <si>
-    <t>A3: 审核状态回滚至 PENDING</t>
-  </si>
-  <si>
-    <t>A4: 迁移状态恢复 (NONE)</t>
-  </si>
-  <si>
-    <t>A5: 删除 MySQL 记录</t>
-  </si>
-  <si>
-    <t>A6: 迁移完成 (进入 COLD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关联风险 ID </t>
-  </si>
-  <si>
-    <t>迁移流程</t>
-  </si>
-  <si>
-    <t xml:space="preserve">标准路径：验证从 APPROVED 和 REJECTED 经 MIGRATING 到 COLD 的完整迁移路径 </t>
-  </si>
-  <si>
-    <t>RSK-1.1.001 / 1.2.002</t>
-  </si>
-  <si>
-    <t>迁移逻辑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阈值拦截：验证评论数 &gt; 2000 时，从 MIGRATING 回滚至原状态 </t>
-  </si>
-  <si>
-    <t>RSK-1.1.004 / 1.4.001</t>
-  </si>
-  <si>
-    <t>事务异常</t>
-  </si>
-  <si>
-    <t xml:space="preserve">写入失败回滚：验证 HBase 写入/校验失败时，事务回滚并恢复原状态 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">状态保护：验证 MIGRATING 状态下拒绝评论/点赞/修改等业务请求 </t>
-  </si>
-  <si>
-    <t>自愈机制</t>
-  </si>
-  <si>
-    <t xml:space="preserve">幂等自愈：验证迁移中断（如 MySQL 未删但 HBase 已有）后的断点续传逻辑 </t>
-  </si>
-  <si>
-    <t>RSK-1.1.003 / 1.4.002</t>
-  </si>
-  <si>
-    <t>恢复流程</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主动激活：验证从 COLD 状态通过 RESTORE 事件写回 MySQL 并删除 HBase 记录 </t>
-  </si>
-  <si>
-    <t>RSK-1.2.003 / 1.3.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">隐式触发：验证列表查询热数据不足时，触发冷数据补齐及异步恢复 </t>
-  </si>
-  <si>
-    <t>RSK-1.3.002 / 1.5.001</t>
-  </si>
-  <si>
-    <t>审核逻辑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">审核流转：验证 PENDING 状态经管理员审核转向 APPROVED 或 REJECTED </t>
-  </si>
-  <si>
-    <t>TCI-STT-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内容修改回滚：验证已审核动态（APPROVED/REJECTED）修改后一律回滚至 PENDING </t>
-  </si>
-  <si>
-    <t>TCI-STT-11</t>
-  </si>
-  <si>
-    <t>生命周期</t>
-  </si>
-  <si>
-    <t xml:space="preserve">多阶段删除：验证 ACTIVE、MIGRATING、COLD 各阶段下的物理删除及归档清理 </t>
-  </si>
-  <si>
-    <t>TCI-STT-12</t>
-  </si>
-  <si>
-    <t>验证动态从冷数据迁回sql后，迁移状态修改为NONE，审核状态保持不变</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.4.003</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.4.004</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_access_time没有更新，最近被访问过的帖子错误进入冷库</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.5.003</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.5.004</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">状态保护：验证 MIGRATING 状态下拒绝评论/点赞/修改内容/修改审核状态等业务请求 </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.3.001/RSK-1.3.008</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.5.001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1102,1396 +2483,39 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>1.3.007/ RSK-1.3.009</t>
-    </r>
-  </si>
-  <si>
-    <t>TCI-STT-13</t>
-  </si>
-  <si>
-    <t>验证审核状态为PENDING的动态不会进行迁移</t>
-  </si>
-  <si>
-    <t>决策逻辑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">验证 HBase 写入异常触发的完整事务回滚 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">验证 HBase 虚假成功（Put 成功但校验失败）的拦截逻辑 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">验证 MySQL 删除阶段超时导致的 MIGRATING 状态遗留场景 </t>
-  </si>
-  <si>
-    <t>TCI-BVA-01-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">评论数临界点：0 条（空数据正常迁移验证） </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSK-1.4.002 / 1.1.004  </t>
-  </si>
-  <si>
-    <t>TCI-BVA-01-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">评论数临界点：1999 条（接近阈值的正常迁移） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-01-C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">评论数临界点：2000 条（迁移阈值上限验证） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-01-D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">评论数临界点：2001 条（触发拦截拦截验证） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-02-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REJECTED 状态时间边界：71h（热数据状态，不迁移） </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSK-1.1.005  </t>
-  </si>
-  <si>
-    <t>TCI-BVA-02-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REJECTED 状态时间边界：72h（临界点，执行迁移） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-02-C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REJECTED 状态时间边界：73h（冷数据状态，执行迁移） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-03-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPROVED 状态时间边界：167h（热数据状态，不迁移） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-03-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPROVED 状态时间边界：168h（临界点，执行迁移） </t>
-  </si>
-  <si>
-    <t>TCI-BVA-03-C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APPROVED 状态时间边界：169h（冷数据状态，执行迁移） </t>
-  </si>
-  <si>
-    <t>用例 ID</t>
-  </si>
-  <si>
-    <t>关联 TCI ID</t>
-  </si>
-  <si>
-    <t>标准冷迁移路径</t>
-  </si>
-  <si>
-    <t>动态状态为 APPROVED/REJECTED，评论数 &lt; 2000，满足时间阈值</t>
-  </si>
-  <si>
-    <r>
-      <t>触发定时迁移任务，检查数据库及</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>状态</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>状态经历</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE-&gt;MIGRATING-&gt;DELETED(COLD)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MySQL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录消失，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>存在归档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>评论数超限拦截</t>
-  </si>
-  <si>
-    <t>动态状态为 NONE，满足时间阈值，但评论数 = 2001</t>
-  </si>
-  <si>
-    <t>触发定时迁移任务</t>
-  </si>
-  <si>
-    <r>
-      <t>状态瞬时变为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> MIGRATING </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>后回滚为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MySQL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录保留，不写入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> HBase </t>
-    </r>
-  </si>
-  <si>
-    <t>写入失败回滚</t>
-  </si>
-  <si>
-    <t>动态符合迁移条件</t>
-  </si>
-  <si>
-    <r>
-      <t>触发任务，模拟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>连接超时或写入失败</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>事务回滚，状态恢复为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE </t>
-    </r>
-  </si>
-  <si>
-    <t>MIGRATING 状态保护</t>
-  </si>
-  <si>
-    <t>动态处于 MIGRATING 状态</t>
-  </si>
-  <si>
-    <t>用户尝试评论、点赞或修改该动态</t>
-  </si>
-  <si>
-    <r>
-      <t>系统抛出业务异常，拒绝请求，数据库无数据变更</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>幂等自愈(断点续传)</t>
-  </si>
-  <si>
-    <t>状态为 MIGRATING，HBase 已有数据但 MySQL 未删</t>
-  </si>
-  <si>
-    <t>再次触发定时任务</t>
-  </si>
-  <si>
-    <r>
-      <t>检测到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>已有数据，跳过写入直接删除</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> MySQL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，进入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> COLD </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>动态处于 COLD 状态</t>
-  </si>
-  <si>
-    <r>
-      <t>用户在前端点击激活</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>恢复</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>发送</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> RESTORE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>事件，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MySQL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>插入数据（状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>），</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录删除</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>列表查询隐式恢复</t>
-  </si>
-  <si>
-    <t>热数据页不足，COLD 库中有数据</t>
-  </si>
-  <si>
-    <t>用户访问动态列表页</t>
-  </si>
-  <si>
-    <r>
-      <t>返回热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>冷混合数据，后台异步触发冷数据恢复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>访问时间更新</t>
-  </si>
-  <si>
-    <t>状态为 NONE，last_access 为 6d 前</t>
-  </si>
-  <si>
-    <t>用户查看动态详情</t>
-  </si>
-  <si>
-    <r>
-      <t>状态保持</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">last_access_time </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>更新为当前时间</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>审核流转路径</t>
-  </si>
-  <si>
-    <t>动态为 PENDING 状态</t>
-  </si>
-  <si>
-    <t>管理员分别执行审核通过和拒绝操作</t>
-  </si>
-  <si>
-    <r>
-      <t>状态分别流向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE(APPROVED) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE(REJECTED) </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-STT-10</t>
-  </si>
-  <si>
-    <t>修改内容状态重置</t>
-  </si>
-  <si>
-    <t>状态为 APPROVED/REJECTED</t>
-  </si>
-  <si>
-    <t>用户修改动态内容</t>
-  </si>
-  <si>
-    <r>
-      <t>无论原状态为何，一律变回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> PENDING </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>状态并隐藏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-STT-11</t>
-  </si>
-  <si>
-    <t>生命周期物理删除</t>
-  </si>
-  <si>
-    <t>动态处于任意阶段（ACTIVE/COLD等）</t>
-  </si>
-  <si>
-    <t>用户执行删除操作</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">MySQL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>记录删除，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>归档同步清理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-STT-12</t>
-  </si>
-  <si>
-    <t>恢复后状态保持</t>
-  </si>
-  <si>
-    <t>动态从 COLD 恢复</t>
-  </si>
-  <si>
-    <t>执行恢复流程</t>
-  </si>
-  <si>
-    <r>
-      <t>迁移状态变回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，原审核状态（如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> REJECTED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）保持不变</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-STT-13</t>
-  </si>
-  <si>
-    <t>审核中拦截</t>
-  </si>
-  <si>
-    <t>动态状态为 PENDING</t>
-  </si>
-  <si>
-    <r>
-      <t>即使满足时间条件，也不进入迁移流程</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>HBase 写入异常回滚</t>
-  </si>
-  <si>
-    <t>符合 Rule 6 场景</t>
-  </si>
-  <si>
-    <r>
-      <t>手动关闭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> HBase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>服务后执行迁移</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>事务感知异常并回滚，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MySQL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>状态回滚为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> NONE </t>
-    </r>
-  </si>
-  <si>
-    <t>虚假成功校验</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mock </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>环境下</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Put </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>成功但</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> exists </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>校验返回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> false</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>触发校验失败异常，事务回滚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>MySQL 删除超时</t>
-  </si>
-  <si>
-    <t>符合 Rule 7 场景</t>
-  </si>
-  <si>
-    <t>对目标行加锁模拟死锁或超时</t>
-  </si>
-  <si>
-    <r>
-      <t>状态保持为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> MIGRATING</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，等待下次重试</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-BVA-01-A</t>
-  </si>
-  <si>
-    <t>评论数下限(0)</t>
-  </si>
-  <si>
-    <t>评论数 = 0</t>
-  </si>
-  <si>
-    <r>
-      <t>正常迁移</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-BVA-01-B</t>
-  </si>
-  <si>
-    <t>评论数临界(1999)</t>
-  </si>
-  <si>
-    <t>评论数 = 1999</t>
-  </si>
-  <si>
-    <t>TC-BVA-01-C</t>
-  </si>
-  <si>
-    <t>评论数阈值(2000)</t>
-  </si>
-  <si>
-    <t>评论数 = 2000</t>
-  </si>
-  <si>
-    <t>TC-BVA-01-D</t>
-  </si>
-  <si>
-    <t>评论数超限(2001)</t>
-  </si>
-  <si>
-    <t>评论数 = 2001</t>
-  </si>
-  <si>
-    <r>
-      <t>触发拦截，状态回滚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-BVA-02-A</t>
-  </si>
-  <si>
-    <t>REJ 状态时间(71h)</t>
-  </si>
-  <si>
-    <t>REJECTED 状态满 71h</t>
-  </si>
-  <si>
-    <r>
-      <t>热数据状态，跳过迁移</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-BVA-02-B</t>
-  </si>
-  <si>
-    <t>REJ 状态时间(72h)</t>
-  </si>
-  <si>
-    <t>REJECTED 状态满 72h</t>
-  </si>
-  <si>
-    <r>
-      <t>达到阈值，开始迁移</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-BVA-02-C</t>
-  </si>
-  <si>
-    <t>REJ 状态时间(73h)</t>
-  </si>
-  <si>
-    <t>REJECTED 状态满 73h</t>
-  </si>
-  <si>
-    <r>
-      <t>超过阈值，开始迁移</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t>TC-BVA-03-A</t>
-  </si>
-  <si>
-    <t>APP 状态时间(167h)</t>
-  </si>
-  <si>
-    <t>APPROVED 状态满 167h</t>
-  </si>
-  <si>
-    <t>TC-BVA-03-B</t>
-  </si>
-  <si>
-    <t>APP 状态时间(168h)</t>
-  </si>
-  <si>
-    <t>APPROVED 状态满 168h</t>
-  </si>
-  <si>
-    <t>APP 状态时间(169h)</t>
-  </si>
-  <si>
-    <t>APPROVED 状态满 169h</t>
-  </si>
-  <si>
-    <t>TCI-STT-14</t>
+      <t>1.1.006/ RSK-1.1.007</t>
+    </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">RSK-1.3.010 </t>
+    <t>数据一致性</t>
+  </si>
+  <si>
+    <t>数据一致性</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>审核逻辑</t>
+    <t>数据完整性</t>
+  </si>
+  <si>
+    <t>系统稳定性</t>
+  </si>
+  <si>
+    <t>系统稳定性</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>只有 APPROVED (已通过) 状态的内容才对他人可见</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>TC-STT-14</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>审核中不可见</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用用户接口获取所有动态</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>动态状态为 PENDING</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>状态为 PENDING的动态不可见</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>风险 ID</t>
-  </si>
-  <si>
-    <t>Tech Risk</t>
-  </si>
-  <si>
-    <t>Bus. Risk</t>
-  </si>
-  <si>
-    <t>Risk Pri. #</t>
-  </si>
-  <si>
-    <t>迁移单个老动态到 HBase</t>
-  </si>
-  <si>
-    <t>HBase 写入失败或验证失败导致迁移中断</t>
-  </si>
-  <si>
-    <t>HBase 写入成功但 MySQL 删除失败，导致冷热数据重复</t>
-  </si>
-  <si>
-    <t>冷迁移时 HBase 写入失败，同时 MySQL 错误删除所有数据</t>
-  </si>
-  <si>
-    <t>HBase 未写入评论/点赞数据，MySQL 已删除导致数据丢失</t>
-  </si>
-  <si>
-    <t>动态按审核状态分阶梯迁移</t>
-  </si>
-  <si>
-    <t>状态判断逻辑错误，导致 PENDING 动态误迁移或时间错误</t>
-  </si>
-  <si>
-    <t>超过评论阈值未恢复 NONE，无法再次进入迁移流程</t>
-  </si>
-  <si>
-    <t>超过阈值恢复至 NONE 操作失败，帖子被锁定 24 小时</t>
-  </si>
-  <si>
-    <t>MIGRATING 帖子在列表中隐形，用户无法发现</t>
-  </si>
-  <si>
-    <t>未通过审核内容被他人通过接口或列表查询获取</t>
-  </si>
-  <si>
-    <t>恢复时 HBase 读取失败，冷数据无法完整恢复</t>
-  </si>
-  <si>
-    <t>恢复时 MySQL 插入成功但评论/点赞插入失败</t>
-  </si>
-  <si>
-    <t>恢复过程中 HBase 读取异常，动态恢复但相关数据丢失</t>
-  </si>
-  <si>
-    <t>恢复后状态未正确设为 NONE，导致动态仍隐形</t>
-  </si>
-  <si>
-    <t>用户查询触发恢复与定时任务重试并发冲突</t>
-  </si>
-  <si>
-    <t>用户点击激活时 MQ 恢复事件发送或处理失败</t>
-  </si>
-  <si>
-    <t>恢复过程中审核状态变更，导致状态机冲突</t>
-  </si>
-  <si>
-    <t>MIGRATING 动态仍被允许加载/评论/点赞/修改</t>
-  </si>
-  <si>
-    <t>状态遗留后未重试，数据在冷热库间“失踪”</t>
-  </si>
-  <si>
-    <t>定时任务执行失败，遗留数据无法自动重试</t>
-  </si>
-  <si>
-    <t>访问冷动态查询回源</t>
-  </si>
-  <si>
-    <t>HBase 宕机时冷动态查询请求直接失败</t>
-  </si>
-  <si>
-    <t>NONE 状态才允许更新审核</t>
-  </si>
-  <si>
-    <t>迁移中状态被修改，导致数据不一致或逻辑违例</t>
-  </si>
-  <si>
-    <t>彻底删除动态</t>
-  </si>
-  <si>
-    <t>用户删除</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>迁移中拒绝点赞/评论/修改操作</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户修改动态内容</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改后审核状态未及时回退，违规内容绕过审核公开</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>仅通过审核的内容对他人可见</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>风险类别</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data Consistency(数据一致性)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data Integrity(数据完整性)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>System Stability(系统稳定性)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Functionality &amp; Availability(功能可用性)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Concurrency Control(并发控制)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>已修复，所有核心单元测试全部通过</t>
+    <t>功能可用性</t>
+  </si>
+  <si>
+    <t>RSK-1.4.005</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2875,7 +2899,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2889,7 +2913,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3188,19 +3212,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="42.6328125" customWidth="1"/>
-    <col min="5" max="5" width="56.36328125" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="42.6328125" customWidth="1"/>
+    <col min="6" max="6" width="56.36328125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -3208,10 +3232,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>2</v>
@@ -3220,30 +3244,33 @@
         <v>3</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>479</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>6</v>
@@ -3257,22 +3284,25 @@
       <c r="I2" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>164</v>
+        <v>531</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>8</v>
@@ -3286,22 +3316,25 @@
       <c r="I3" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="D4" s="14" t="s">
-        <v>164</v>
+        <v>531</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>14</v>
@@ -3315,8 +3348,11 @@
       <c r="I4" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
@@ -3327,10 +3363,10 @@
         <v>13</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>164</v>
+        <v>531</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>14</v>
@@ -3344,22 +3380,25 @@
       <c r="I5" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>164</v>
+        <v>531</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>6</v>
@@ -3373,51 +3412,57 @@
       <c r="I6" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="14">
-        <v>4</v>
-      </c>
-      <c r="H7" s="14">
-        <v>5</v>
-      </c>
       <c r="I7" s="14">
+        <v>12</v>
+      </c>
+      <c r="J7" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>494</v>
+        <v>25</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>10</v>
+        <v>518</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>167</v>
+        <v>531</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>6</v>
@@ -3426,56 +3471,62 @@
         <v>4</v>
       </c>
       <c r="H8" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="14">
+        <v>16</v>
+      </c>
+      <c r="J8" s="14">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>26</v>
+        <v>480</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>167</v>
+        <v>533</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="14">
         <v>5</v>
       </c>
       <c r="I9" s="14">
+        <v>20</v>
+      </c>
+      <c r="J9" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>26</v>
+        <v>480</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>167</v>
+        <v>533</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>6</v>
@@ -3484,172 +3535,190 @@
         <v>4</v>
       </c>
       <c r="H10" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="14">
+        <v>20</v>
+      </c>
+      <c r="J10" s="14">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>263</v>
+        <v>24</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>519</v>
+        <v>25</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>167</v>
+        <v>533</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>265</v>
+        <v>490</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>5</v>
+      </c>
+      <c r="I11" s="14">
+        <v>15</v>
+      </c>
+      <c r="J11" s="14">
         <v>2</v>
       </c>
-      <c r="H11" s="14">
-        <v>1</v>
-      </c>
-      <c r="I11" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>521</v>
+        <v>25</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>170</v>
+        <v>533</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>512</v>
+        <v>491</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="14">
         <v>4</v>
       </c>
       <c r="I12" s="14">
+        <v>16</v>
+      </c>
+      <c r="J12" s="14">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>21</v>
+        <v>519</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>170</v>
+        <v>533</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>22</v>
+        <v>492</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G13" s="14">
         <v>4</v>
       </c>
       <c r="H13" s="14">
+        <v>5</v>
+      </c>
+      <c r="I13" s="14">
+        <v>20</v>
+      </c>
+      <c r="J13" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="14">
         <v>3</v>
       </c>
-      <c r="I13" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="14">
+      <c r="H14" s="14">
         <v>4</v>
-      </c>
-      <c r="H14" s="14">
-        <v>3</v>
       </c>
       <c r="I14" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>17</v>
+        <v>506</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>18</v>
+        <v>520</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>503</v>
+        <v>34</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
         <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>4</v>
       </c>
       <c r="I15" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>26</v>
+        <v>502</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>29</v>
+        <v>521</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>6</v>
@@ -3658,143 +3727,158 @@
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="J16" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>170</v>
+        <v>535</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="14">
         <v>4</v>
       </c>
       <c r="I17" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="J17" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>517</v>
+        <v>36</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>170</v>
+        <v>534</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" s="14">
         <v>4</v>
       </c>
       <c r="I18" s="14">
+        <v>8</v>
+      </c>
+      <c r="J18" s="14">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="C19" s="14" t="s">
-        <v>260</v>
+        <v>522</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>170</v>
+        <v>534</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="J19" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>258</v>
+        <v>39</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>259</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>170</v>
+        <v>534</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
         <v>5</v>
       </c>
       <c r="I20" s="14">
+        <v>10</v>
+      </c>
+      <c r="J20" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>266</v>
+        <v>16</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>522</v>
+        <v>17</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>267</v>
+        <v>523</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>170</v>
+        <v>534</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>6</v>
@@ -3803,187 +3887,188 @@
         <v>3</v>
       </c>
       <c r="H21" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="J21" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>11</v>
+        <v>255</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>12</v>
+        <v>504</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>15</v>
+        <v>537</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>502</v>
+        <v>256</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14">
+        <v>1</v>
+      </c>
+      <c r="I22" s="14">
+        <v>2</v>
+      </c>
+      <c r="J22" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>536</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="14">
         <v>4</v>
       </c>
-      <c r="I22" s="14">
+      <c r="H23" s="14">
+        <v>3</v>
+      </c>
+      <c r="I23" s="14">
+        <v>12</v>
+      </c>
+      <c r="J23" s="14">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="14">
-        <v>4</v>
-      </c>
-      <c r="I23" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>14</v>
       </c>
       <c r="G24" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H24" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="14">
+        <v>12</v>
+      </c>
+      <c r="J24" s="14">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>40</v>
+        <v>253</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>31</v>
+        <v>525</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="14">
         <v>5</v>
       </c>
       <c r="I25" s="14">
+        <v>15</v>
+      </c>
+      <c r="J25" s="14">
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>20</v>
+        <v>507</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>23</v>
+        <v>526</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>175</v>
+        <v>536</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>24</v>
+        <v>508</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G26" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I26" s="14">
+        <v>15</v>
+      </c>
+      <c r="J26" s="14">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>510</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="25">
-        <v>3</v>
-      </c>
-      <c r="H27" s="25">
-        <v>4</v>
-      </c>
-      <c r="I27" s="25">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -3993,8 +4078,9 @@
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24"/>
@@ -4004,8 +4090,9 @@
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
       <c r="I29" s="24"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="24"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
       <c r="B30" s="24"/>
       <c r="C30" s="24"/>
@@ -4015,10 +4102,11 @@
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
       <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
     </row>
   </sheetData>
-  <sortState ref="A2:I27">
-    <sortCondition ref="C2:C27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
+    <sortCondition ref="C3:C26"/>
   </sortState>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4027,7 +4115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4037,324 +4125,324 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>51</v>
-      </c>
       <c r="E6" s="15" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>281</v>
-      </c>
       <c r="F8" s="15" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="15" t="s">
+      <c r="F12" s="15" t="s">
         <v>63</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>66</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>54</v>
-      </c>
       <c r="E16" s="15" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -4366,163 +4454,163 @@
     </row>
     <row r="20" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="E20" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B22" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="D22" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E23" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="G23" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="G24" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="19" t="s">
         <v>72</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -4534,158 +4622,158 @@
     </row>
     <row r="27" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="18" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -4965,7 +5053,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4978,64 +5066,64 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>79</v>
-      </c>
       <c r="E1" s="17" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>6</v>
@@ -5046,200 +5134,200 @@
     </row>
     <row r="5" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="C5" s="19" t="s">
-        <v>333</v>
+        <v>527</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>34</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>341</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>89</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>90</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>18</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>267</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>264</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>351</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>6</v>
@@ -5250,13 +5338,13 @@
     </row>
     <row r="17" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>6</v>
@@ -5267,13 +5355,13 @@
     </row>
     <row r="18" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>6</v>
@@ -5284,172 +5372,172 @@
     </row>
     <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5459,7 +5547,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5472,562 +5560,562 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>104</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>112</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -6037,7 +6125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6048,19 +6136,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -6071,13 +6159,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6088,13 +6176,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6105,13 +6193,13 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -6122,13 +6210,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6139,13 +6227,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6156,13 +6244,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -6173,13 +6261,13 @@
         <v>10</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -6190,13 +6278,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -6207,13 +6295,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -6224,13 +6312,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -6241,13 +6329,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6258,13 +6346,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -6275,13 +6363,13 @@
         <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6289,220 +6377,220 @@
         <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="C21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -6512,7 +6600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6525,42 +6613,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="84" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>151</v>
-      </c>
       <c r="F2" s="27" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -6570,7 +6658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6582,44 +6670,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6630,86 +6718,86 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>526</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -6723,55 +6811,55 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -6782,58 +6870,58 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6844,58 +6932,58 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -6906,16 +6994,16 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -6926,73 +7014,73 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D34" s="8"/>
     </row>
@@ -7004,109 +7092,109 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D43" s="8"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D44" s="8"/>
     </row>
@@ -7118,61 +7206,61 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D50" s="8"/>
     </row>
@@ -7184,73 +7272,73 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D52" s="8"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D57" s="8"/>
     </row>
@@ -7262,25 +7350,25 @@
     </row>
     <row r="59" spans="1:4" ht="28" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D59" s="8"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D60" s="8"/>
     </row>
@@ -7292,73 +7380,73 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D64" s="8"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D65" s="8"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D66" s="8"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D67" s="8"/>
     </row>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEEBDC8-8028-4317-BEB4-63049FA46F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95302952-FF82-4782-86BA-33FB8C07A8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="539">
   <si>
     <t>需求 ID</t>
   </si>
@@ -2509,6 +2509,10 @@
   </si>
   <si>
     <t>RSK-1.4.005</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.4.006</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3832,100 +3836,100 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>30</v>
+        <v>523</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>534</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>17</v>
+        <v>504</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="D21" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14">
+        <v>2</v>
+      </c>
+      <c r="J21" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="E22" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>6</v>
-      </c>
-      <c r="G21" s="14">
-        <v>3</v>
-      </c>
-      <c r="H21" s="14">
-        <v>4</v>
-      </c>
-      <c r="I21" s="14">
-        <v>12</v>
-      </c>
-      <c r="J21" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>537</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>8</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4106,7 +4110,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
-    <sortCondition ref="C3:C26"/>
+    <sortCondition ref="C20:C26"/>
   </sortState>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\Pet-Care-Ecosystem\Documents\HBase\Moment冷热分离测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95302952-FF82-4782-86BA-33FB8C07A8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="545">
   <si>
     <t>需求 ID</t>
   </si>
@@ -1010,9 +1009,6 @@
   </si>
   <si>
     <t xml:space="preserve">主动激活：验证从 COLD 状态通过 RESTORE 事件写回 MySQL 并删除 HBase 记录 </t>
-  </si>
-  <si>
-    <t>RSK-1.2.003 / 1.3.006</t>
   </si>
   <si>
     <t xml:space="preserve">隐式触发：验证列表查询热数据不足时，触发冷数据补齐及异步恢复 </t>
@@ -2425,10 +2421,6 @@
   </si>
   <si>
     <t>RSK-1.1.007</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>RSK-1.2.006</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -2515,11 +2507,37 @@
     <t>RSK-1.4.006</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>RSK-1.2.003 / 1.1.006</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.2.006</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试套组</t>
+  </si>
+  <si>
+    <t>TS-01</t>
+  </si>
+  <si>
+    <t>TS-02</t>
+  </si>
+  <si>
+    <t>TS-03</t>
+  </si>
+  <si>
+    <t>TS-04</t>
+  </si>
+  <si>
+    <t>TS-05</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2619,7 +2637,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -2816,15 +2834,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -2832,7 +2861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2909,15 +2938,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3216,19 +3251,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="42.6328125" customWidth="1"/>
-    <col min="6" max="6" width="56.36328125" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="5" max="5" width="58.26953125" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" customWidth="1"/>
+    <col min="8" max="8" width="12.08984375" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -3236,10 +3274,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>2</v>
@@ -3248,16 +3286,16 @@
         <v>3</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>477</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="I1" s="14" t="s">
-        <v>479</v>
-      </c>
       <c r="J1" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3265,16 +3303,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>6</v>
@@ -3292,21 +3330,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>8</v>
@@ -3335,10 +3373,10 @@
         <v>37</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F4" s="14" t="s">
         <v>14</v>
@@ -3356,7 +3394,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
@@ -3367,10 +3405,10 @@
         <v>13</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>14</v>
@@ -3388,21 +3426,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>251</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>252</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>6</v>
@@ -3428,13 +3466,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>14</v>
@@ -3460,13 +3498,13 @@
         <v>25</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>6</v>
@@ -3484,21 +3522,21 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>6</v>
@@ -3516,21 +3554,21 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>6</v>
@@ -3559,10 +3597,10 @@
         <v>26</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>6</v>
@@ -3591,10 +3629,10 @@
         <v>27</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>6</v>
@@ -3612,7 +3650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>24</v>
       </c>
@@ -3620,13 +3658,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>6</v>
@@ -3649,7 +3687,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>33</v>
@@ -3658,7 +3696,7 @@
         <v>84</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>6</v>
@@ -3681,10 +3719,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>84</v>
@@ -3713,16 +3751,16 @@
         <v>254</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>84</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>6</v>
@@ -3740,7 +3778,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>11</v>
       </c>
@@ -3751,10 +3789,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>6</v>
@@ -3783,10 +3821,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>6</v>
@@ -3812,13 +3850,13 @@
         <v>25</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>14</v>
@@ -3836,7 +3874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>16</v>
       </c>
@@ -3844,13 +3882,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>6</v>
@@ -3868,18 +3906,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>255</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>256</v>
@@ -3905,16 +3943,16 @@
         <v>39</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>536</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>500</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>501</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>6</v>
@@ -3943,7 +3981,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>23</v>
@@ -3975,10 +4013,10 @@
         <v>31</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>14</v>
@@ -4001,16 +4039,16 @@
         <v>253</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>6</v>
@@ -4028,21 +4066,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>257</v>
       </c>
       <c r="B26" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>507</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>508</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>6</v>
@@ -4073,16 +4111,16 @@
       <c r="J27" s="25"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
@@ -4096,20 +4134,8 @@
       <c r="I29" s="24"/>
       <c r="J29" s="24"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J26">
+  <sortState ref="A2:J26">
     <sortCondition ref="C20:C26"/>
   </sortState>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -4119,7 +4145,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4398,7 +4424,7 @@
         <v>287</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>52</v>
@@ -5057,13 +5083,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="46.36328125" customWidth="1"/>
+    <col min="3" max="3" width="87" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
@@ -5085,7 +5111,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>80</v>
       </c>
@@ -5102,7 +5128,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
         <v>81</v>
       </c>
@@ -5119,7 +5145,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>82</v>
       </c>
@@ -5136,7 +5162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
         <v>83</v>
       </c>
@@ -5144,16 +5170,16 @@
         <v>84</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>85</v>
       </c>
@@ -5170,7 +5196,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
         <v>86</v>
       </c>
@@ -5184,10 +5210,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>87</v>
       </c>
@@ -5195,13 +5221,13 @@
         <v>326</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5218,86 +5244,86 @@
         <v>14</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>90</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>330</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>331</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>332</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>333</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="19" t="s">
         <v>335</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>336</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>315</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>315</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>6</v>
@@ -5308,19 +5334,19 @@
     </row>
     <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>467</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="C15" s="19" t="s">
         <v>469</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>470</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5328,10 +5354,10 @@
         <v>91</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>341</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>342</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>6</v>
@@ -5340,15 +5366,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
         <v>92</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>6</v>
@@ -5357,15 +5383,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>93</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>6</v>
@@ -5376,182 +5402,183 @@
     </row>
     <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="19" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
         <v>356</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>357</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5564,10 +5591,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>367</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>368</v>
       </c>
       <c r="C1" s="17" t="s">
         <v>101</v>
@@ -5590,16 +5617,16 @@
         <v>80</v>
       </c>
       <c r="C2" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="22" t="s">
         <v>371</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5610,16 +5637,16 @@
         <v>81</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="F3" s="22" t="s">
         <v>375</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5630,16 +5657,16 @@
         <v>82</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="F4" s="22" t="s">
         <v>379</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5650,16 +5677,16 @@
         <v>83</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="22" t="s">
         <v>382</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="F5" s="22" t="s">
         <v>383</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5670,16 +5697,16 @@
         <v>85</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>386</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="F6" s="22" t="s">
         <v>387</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5693,13 +5720,13 @@
         <v>111</v>
       </c>
       <c r="D7" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="E7" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="F7" s="22" t="s">
         <v>390</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5710,16 +5737,16 @@
         <v>87</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>393</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="F8" s="22" t="s">
         <v>394</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -5730,16 +5757,16 @@
         <v>88</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="22" t="s">
         <v>397</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="F9" s="22" t="s">
         <v>398</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -5750,116 +5777,116 @@
         <v>90</v>
       </c>
       <c r="C10" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>400</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="E10" s="22" t="s">
         <v>401</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="F10" s="22" t="s">
         <v>402</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="E11" s="22" t="s">
         <v>406</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="F11" s="22" t="s">
         <v>407</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="C12" s="19" t="s">
+      <c r="D12" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="E12" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="F12" s="23" t="s">
         <v>412</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="E13" s="22" t="s">
         <v>416</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="F13" s="22" t="s">
         <v>417</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="E14" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>421</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>472</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="F15" s="22" t="s">
         <v>474</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>473</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5870,16 +5897,16 @@
         <v>91</v>
       </c>
       <c r="C16" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="E16" s="22" t="s">
         <v>424</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="F16" s="22" t="s">
         <v>425</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -5890,16 +5917,16 @@
         <v>92</v>
       </c>
       <c r="C17" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>424</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="F17" s="22" t="s">
         <v>428</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -5910,216 +5937,216 @@
         <v>93</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>430</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="E18" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="F18" s="22" t="s">
         <v>432</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>435</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>436</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="D20" s="19" t="s">
         <v>439</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>440</v>
       </c>
       <c r="E20" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>441</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>442</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>443</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>444</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="D22" s="19" t="s">
         <v>445</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>446</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>448</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="D23" s="19" t="s">
         <v>449</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>450</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="19" t="s">
         <v>453</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>454</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>456</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="C25" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>457</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>458</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>460</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="C26" s="19" t="s">
+      <c r="D26" s="19" t="s">
         <v>461</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>462</v>
       </c>
       <c r="E26" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="C27" s="19" t="s">
+      <c r="D27" s="19" t="s">
         <v>464</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>465</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C28" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="D28" s="19" t="s">
         <v>466</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>467</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>121</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -6129,16 +6156,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="41.81640625" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="10" max="10" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>123</v>
       </c>
@@ -6154,8 +6183,17 @@
       <c r="E1" s="6" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -6171,8 +6209,17 @@
       <c r="E2" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H2" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -6188,8 +6235,15 @@
       <c r="E3" s="5" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H3" s="29"/>
+      <c r="I3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -6205,8 +6259,15 @@
       <c r="E4" s="5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H4" s="29"/>
+      <c r="I4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -6222,59 +6283,87 @@
       <c r="E5" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H5" s="29"/>
+      <c r="I5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="H6" s="29"/>
+      <c r="I6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -6282,16 +6371,23 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -6299,174 +6395,248 @@
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="H10" s="28"/>
+      <c r="I10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>541</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="29"/>
+      <c r="I13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="29"/>
+      <c r="I14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" s="28"/>
+      <c r="I15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>542</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" s="29"/>
+      <c r="I17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="29"/>
+      <c r="I18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H19" s="29"/>
+      <c r="I19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>86</v>
@@ -6477,47 +6647,70 @@
       <c r="E20" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H20" s="29"/>
+      <c r="I20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="H21" s="28"/>
+      <c r="I21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>543</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>85</v>
@@ -6528,13 +6721,20 @@
       <c r="E23" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H23" s="29"/>
+      <c r="I23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>94</v>
@@ -6545,47 +6745,70 @@
       <c r="E24" s="5" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H24" s="29"/>
+      <c r="I24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="H25" s="28"/>
+      <c r="I25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>86</v>
@@ -6596,15 +6819,32 @@
       <c r="E27" s="5" t="s">
         <v>137</v>
       </c>
+      <c r="H27" s="28"/>
+      <c r="I27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="A2:E27">
+    <sortCondition ref="B2:B27"/>
+  </sortState>
+  <mergeCells count="5">
+    <mergeCell ref="H2:H10"/>
+    <mergeCell ref="H11:H15"/>
+    <mergeCell ref="H16:H21"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="H26:H27"/>
+  </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6651,8 +6891,8 @@
       <c r="E2" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F2" s="27" t="s">
-        <v>516</v>
+      <c r="F2" s="26" t="s">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -6662,7 +6902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6741,8 +6981,8 @@
       <c r="B6" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>511</v>
+      <c r="C6" s="26" t="s">
+        <v>510</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>163</v>
@@ -6755,8 +6995,8 @@
       <c r="B7" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>512</v>
+      <c r="C7" s="26" t="s">
+        <v>511</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>165</v>
@@ -6769,8 +7009,8 @@
       <c r="B8" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>515</v>
+      <c r="C8" s="26" t="s">
+        <v>514</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>167</v>
@@ -6783,8 +7023,8 @@
       <c r="B9" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>513</v>
+      <c r="C9" s="26" t="s">
+        <v>512</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>169</v>
@@ -6797,8 +7037,8 @@
       <c r="B10" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>514</v>
+      <c r="C10" s="26" t="s">
+        <v>513</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>171</v>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -9,23 +9,25 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="4"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
-    <sheet name="逻辑模型" sheetId="3" r:id="rId2"/>
-    <sheet name="覆盖项清单" sheetId="4" r:id="rId3"/>
-    <sheet name="测试用例" sheetId="5" r:id="rId4"/>
-    <sheet name="追溯矩阵" sheetId="6" r:id="rId5"/>
-    <sheet name="缺陷报告" sheetId="7" r:id="rId6"/>
-    <sheet name="ID说明与列名解释" sheetId="1" r:id="rId7"/>
+    <sheet name="原始STT" sheetId="8" r:id="rId2"/>
+    <sheet name="增补STT" sheetId="10" r:id="rId3"/>
+    <sheet name="决策表DT" sheetId="3" r:id="rId4"/>
+    <sheet name="覆盖项清单" sheetId="4" r:id="rId5"/>
+    <sheet name="测试用例" sheetId="5" r:id="rId6"/>
+    <sheet name="追溯矩阵" sheetId="6" r:id="rId7"/>
+    <sheet name="缺陷报告" sheetId="7" r:id="rId8"/>
+    <sheet name="ID说明与列名解释" sheetId="1" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="563">
   <si>
     <t>需求 ID</t>
   </si>
@@ -147,9 +149,6 @@
     <t>REQ-M7</t>
   </si>
   <si>
-    <t>状态转移表 (STT)</t>
-  </si>
-  <si>
     <t>当前状态</t>
   </si>
   <si>
@@ -180,9 +179,6 @@
     <t>MIGRATING</t>
   </si>
   <si>
-    <t>M-1</t>
-  </si>
-  <si>
     <t>鉴权通过</t>
   </si>
   <si>
@@ -198,9 +194,6 @@
     <t>comments &gt; 2000</t>
   </si>
   <si>
-    <t>M-1/M-6</t>
-  </si>
-  <si>
     <t>COLD (ARCHIVED)</t>
   </si>
   <si>
@@ -216,24 +209,12 @@
     <t>发送MQ，异步写回MySQL后删HBase</t>
   </si>
   <si>
-    <t>M-4</t>
-  </si>
-  <si>
     <t>列表查询</t>
   </si>
   <si>
     <t>热数据页不足</t>
   </si>
   <si>
-    <t>M-3B</t>
-  </si>
-  <si>
-    <t>决策表 (DT)</t>
-  </si>
-  <si>
-    <t>条件/动作</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -828,24 +809,15 @@
     <t>原子更新 migration_status</t>
   </si>
   <si>
-    <t>M-1/M-1S</t>
-  </si>
-  <si>
     <t>last_access &gt; 3d</t>
   </si>
   <si>
-    <t>M-1/M1-S</t>
-  </si>
-  <si>
     <t>用户修改内容</t>
   </si>
   <si>
     <t>重置审核状态，隐藏动态</t>
   </si>
   <si>
-    <t>M-10</t>
-  </si>
-  <si>
     <t>重置审核状态</t>
   </si>
   <si>
@@ -873,18 +845,12 @@
     <t>拒绝请求 (抛出异常)</t>
   </si>
   <si>
-    <t>M-5/M-8</t>
-  </si>
-  <si>
     <t>用户触发 RESTORE 事件</t>
   </si>
   <si>
     <t>发送 MQ，写回后删 HBase</t>
   </si>
   <si>
-    <t>M4</t>
-  </si>
-  <si>
     <t>补齐数据并异步恢复</t>
   </si>
   <si>
@@ -894,9 +860,6 @@
     <t>物理删除 MySQL 记录，清理 HBase</t>
   </si>
   <si>
-    <t>M-9</t>
-  </si>
-  <si>
     <t>R1 (热数据)</t>
   </si>
   <si>
@@ -946,9 +909,6 @@
   </si>
   <si>
     <t>C6: MySQL 删除结果</t>
-  </si>
-  <si>
-    <t>动作 (Actions)</t>
   </si>
   <si>
     <t>A1: 获取/保持锁定</t>
@@ -2368,10 +2328,6 @@
     <t>彻底删除动态</t>
   </si>
   <si>
-    <t>用户删除</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>迁移中拒绝点赞/评论/修改操作</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -2533,17 +2489,154 @@
   <si>
     <t>TS-05</t>
   </si>
+  <si>
+    <t>用户删除</t>
+  </si>
+  <si>
+    <t>M-9</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应需求ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-3B</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-5/M-8</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1/M-6</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1/M1-S</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1/M-1S</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Undefined</t>
+  </si>
+  <si>
+    <t>M-9</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理删除 MySQL 记录</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1/M-1S</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-9</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理删除 MySQL 记录</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1/M-6</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理删除 MySQL 记录，清理 HBase</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-5/M-8</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>COLD (ARCHIVED)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户删除</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>M-3B</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应需求ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>动作 (Actions)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件/动作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2569,14 +2662,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2628,6 +2713,42 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2637,7 +2758,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2725,45 +2846,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -2823,17 +2905,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -2858,18 +2929,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2878,81 +2950,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3252,14 +3333,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="58.26953125" customWidth="1"/>
-    <col min="6" max="6" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
     <col min="7" max="7" width="10.90625" customWidth="1"/>
     <col min="8" max="8" width="12.08984375" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
@@ -3267,872 +3348,860 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>3</v>
+      </c>
+      <c r="H2" s="12">
+        <v>4</v>
+      </c>
+      <c r="I2" s="12">
+        <v>12</v>
+      </c>
+      <c r="J2" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="12">
+        <v>3</v>
+      </c>
+      <c r="H3" s="12">
+        <v>2</v>
+      </c>
+      <c r="I3" s="12">
+        <v>6</v>
+      </c>
+      <c r="J3" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="12">
+        <v>3</v>
+      </c>
+      <c r="H4" s="12">
+        <v>4</v>
+      </c>
+      <c r="I4" s="12">
+        <v>12</v>
+      </c>
+      <c r="J4" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="12">
+        <v>2</v>
+      </c>
+      <c r="H5" s="12">
+        <v>3</v>
+      </c>
+      <c r="I5" s="12">
+        <v>6</v>
+      </c>
+      <c r="J5" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="12">
+        <v>3</v>
+      </c>
+      <c r="H6" s="12">
+        <v>4</v>
+      </c>
+      <c r="I6" s="12">
+        <v>12</v>
+      </c>
+      <c r="J6" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="12">
+        <v>3</v>
+      </c>
+      <c r="H7" s="12">
+        <v>4</v>
+      </c>
+      <c r="I7" s="12">
+        <v>12</v>
+      </c>
+      <c r="J7" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="12">
+        <v>4</v>
+      </c>
+      <c r="H8" s="12">
+        <v>4</v>
+      </c>
+      <c r="I8" s="12">
+        <v>16</v>
+      </c>
+      <c r="J8" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="12">
+        <v>4</v>
+      </c>
+      <c r="H9" s="12">
+        <v>5</v>
+      </c>
+      <c r="I9" s="12">
+        <v>20</v>
+      </c>
+      <c r="J9" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="12">
+        <v>4</v>
+      </c>
+      <c r="H10" s="12">
+        <v>5</v>
+      </c>
+      <c r="I10" s="12">
+        <v>20</v>
+      </c>
+      <c r="J10" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="12">
+        <v>3</v>
+      </c>
+      <c r="H11" s="12">
+        <v>5</v>
+      </c>
+      <c r="I11" s="12">
+        <v>15</v>
+      </c>
+      <c r="J11" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="12">
+        <v>4</v>
+      </c>
+      <c r="H12" s="12">
+        <v>4</v>
+      </c>
+      <c r="I12" s="12">
+        <v>16</v>
+      </c>
+      <c r="J12" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="12">
+        <v>4</v>
+      </c>
+      <c r="H13" s="12">
+        <v>5</v>
+      </c>
+      <c r="I13" s="12">
+        <v>20</v>
+      </c>
+      <c r="J13" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="12">
+        <v>3</v>
+      </c>
+      <c r="H14" s="12">
+        <v>4</v>
+      </c>
+      <c r="I14" s="12">
+        <v>12</v>
+      </c>
+      <c r="J14" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="12">
+        <v>4</v>
+      </c>
+      <c r="H15" s="12">
+        <v>3</v>
+      </c>
+      <c r="I15" s="12">
+        <v>12</v>
+      </c>
+      <c r="J15" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="12">
+        <v>4</v>
+      </c>
+      <c r="H16" s="12">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12">
+        <v>16</v>
+      </c>
+      <c r="J16" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="12">
+        <v>2</v>
+      </c>
+      <c r="H17" s="12">
+        <v>4</v>
+      </c>
+      <c r="I17" s="12">
+        <v>8</v>
+      </c>
+      <c r="J17" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="12">
+        <v>2</v>
+      </c>
+      <c r="H18" s="12">
+        <v>4</v>
+      </c>
+      <c r="I18" s="12">
+        <v>8</v>
+      </c>
+      <c r="J18" s="12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="12">
+        <v>5</v>
+      </c>
+      <c r="H19" s="12">
+        <v>3</v>
+      </c>
+      <c r="I19" s="12">
+        <v>15</v>
+      </c>
+      <c r="J19" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="12">
+        <v>3</v>
+      </c>
+      <c r="H20" s="12">
+        <v>4</v>
+      </c>
+      <c r="I20" s="12">
+        <v>12</v>
+      </c>
+      <c r="J20" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="12">
+        <v>2</v>
+      </c>
+      <c r="H21" s="12">
+        <v>1</v>
+      </c>
+      <c r="I21" s="12">
+        <v>2</v>
+      </c>
+      <c r="J21" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="12">
+        <v>2</v>
+      </c>
+      <c r="H22" s="12">
+        <v>5</v>
+      </c>
+      <c r="I22" s="12">
+        <v>10</v>
+      </c>
+      <c r="J22" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="12">
+        <v>4</v>
+      </c>
+      <c r="H23" s="12">
+        <v>3</v>
+      </c>
+      <c r="I23" s="12">
+        <v>12</v>
+      </c>
+      <c r="J23" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="12">
+        <v>3</v>
+      </c>
+      <c r="H24" s="12">
+        <v>4</v>
+      </c>
+      <c r="I24" s="12">
+        <v>12</v>
+      </c>
+      <c r="J24" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="12">
+        <v>3</v>
+      </c>
+      <c r="H25" s="12">
+        <v>5</v>
+      </c>
+      <c r="I25" s="12">
+        <v>15</v>
+      </c>
+      <c r="J25" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="D26" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="12">
         <v>3</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>476</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>477</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="H26" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="14">
-        <v>3</v>
-      </c>
-      <c r="H2" s="14">
-        <v>4</v>
-      </c>
-      <c r="I2" s="14">
+      <c r="I26" s="12">
+        <v>15</v>
+      </c>
+      <c r="J26" s="12">
         <v>12</v>
       </c>
-      <c r="J2" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>481</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="14">
-        <v>3</v>
-      </c>
-      <c r="H3" s="14">
-        <v>2</v>
-      </c>
-      <c r="I3" s="14">
-        <v>6</v>
-      </c>
-      <c r="J3" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>497</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="14">
-        <v>3</v>
-      </c>
-      <c r="H4" s="14">
-        <v>4</v>
-      </c>
-      <c r="I4" s="14">
-        <v>12</v>
-      </c>
-      <c r="J4" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>486</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="14">
-        <v>2</v>
-      </c>
-      <c r="H5" s="14">
-        <v>3</v>
-      </c>
-      <c r="I5" s="14">
-        <v>6</v>
-      </c>
-      <c r="J5" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>484</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="14">
-        <v>3</v>
-      </c>
-      <c r="H6" s="14">
-        <v>4</v>
-      </c>
-      <c r="I6" s="14">
-        <v>12</v>
-      </c>
-      <c r="J6" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="14">
-        <v>3</v>
-      </c>
-      <c r="H7" s="14">
-        <v>4</v>
-      </c>
-      <c r="I7" s="14">
-        <v>12</v>
-      </c>
-      <c r="J7" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>517</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>529</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>495</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="14">
-        <v>4</v>
-      </c>
-      <c r="H8" s="14">
-        <v>4</v>
-      </c>
-      <c r="I8" s="14">
-        <v>16</v>
-      </c>
-      <c r="J8" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="14">
-        <v>4</v>
-      </c>
-      <c r="H9" s="14">
-        <v>5</v>
-      </c>
-      <c r="I9" s="14">
-        <v>20</v>
-      </c>
-      <c r="J9" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>479</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>483</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="14">
-        <v>4</v>
-      </c>
-      <c r="H10" s="14">
-        <v>5</v>
-      </c>
-      <c r="I10" s="14">
-        <v>20</v>
-      </c>
-      <c r="J10" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="14">
-        <v>3</v>
-      </c>
-      <c r="H11" s="14">
-        <v>5</v>
-      </c>
-      <c r="I11" s="14">
-        <v>15</v>
-      </c>
-      <c r="J11" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="14">
-        <v>4</v>
-      </c>
-      <c r="H12" s="14">
-        <v>4</v>
-      </c>
-      <c r="I12" s="14">
-        <v>16</v>
-      </c>
-      <c r="J12" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>538</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>531</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="14">
-        <v>4</v>
-      </c>
-      <c r="H13" s="14">
-        <v>5</v>
-      </c>
-      <c r="I13" s="14">
-        <v>20</v>
-      </c>
-      <c r="J13" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>496</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="14">
-        <v>3</v>
-      </c>
-      <c r="H14" s="14">
-        <v>4</v>
-      </c>
-      <c r="I14" s="14">
-        <v>12</v>
-      </c>
-      <c r="J14" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>518</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
-      <c r="H15" s="14">
-        <v>3</v>
-      </c>
-      <c r="I15" s="14">
-        <v>12</v>
-      </c>
-      <c r="J15" s="14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>501</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>519</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>502</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
-      <c r="H16" s="14">
-        <v>4</v>
-      </c>
-      <c r="I16" s="14">
-        <v>16</v>
-      </c>
-      <c r="J16" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="14">
-        <v>2</v>
-      </c>
-      <c r="H17" s="14">
-        <v>4</v>
-      </c>
-      <c r="I17" s="14">
-        <v>8</v>
-      </c>
-      <c r="J17" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="14">
-        <v>2</v>
-      </c>
-      <c r="H18" s="14">
-        <v>4</v>
-      </c>
-      <c r="I18" s="14">
-        <v>8</v>
-      </c>
-      <c r="J18" s="14">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="14">
-        <v>5</v>
-      </c>
-      <c r="H19" s="14">
-        <v>3</v>
-      </c>
-      <c r="I19" s="14">
-        <v>15</v>
-      </c>
-      <c r="J19" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="14">
-        <v>3</v>
-      </c>
-      <c r="H20" s="14">
-        <v>4</v>
-      </c>
-      <c r="I20" s="14">
-        <v>12</v>
-      </c>
-      <c r="J20" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>535</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="14">
-        <v>2</v>
-      </c>
-      <c r="H21" s="14">
-        <v>1</v>
-      </c>
-      <c r="I21" s="14">
-        <v>2</v>
-      </c>
-      <c r="J21" s="14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>499</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="14">
-        <v>5</v>
-      </c>
-      <c r="I22" s="14">
-        <v>10</v>
-      </c>
-      <c r="J22" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="14">
-        <v>4</v>
-      </c>
-      <c r="H23" s="14">
-        <v>3</v>
-      </c>
-      <c r="I23" s="14">
-        <v>12</v>
-      </c>
-      <c r="J23" s="14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="14">
-        <v>3</v>
-      </c>
-      <c r="H24" s="14">
-        <v>4</v>
-      </c>
-      <c r="I24" s="14">
-        <v>12</v>
-      </c>
-      <c r="J24" s="14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>523</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="14">
-        <v>3</v>
-      </c>
-      <c r="H25" s="14">
-        <v>5</v>
-      </c>
-      <c r="I25" s="14">
-        <v>15</v>
-      </c>
-      <c r="J25" s="14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>534</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="14">
-        <v>3</v>
-      </c>
-      <c r="H26" s="14">
-        <v>5</v>
-      </c>
-      <c r="I26" s="14">
-        <v>15</v>
-      </c>
-      <c r="J26" s="14">
-        <v>12</v>
-      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
     </row>
   </sheetData>
   <sortState ref="A2:J26">
@@ -4146,935 +4215,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="8" width="12" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" style="26" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" style="26" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" style="26" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="B1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="F1" s="28" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>268</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="E10" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="B11" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>530</v>
+      </c>
+      <c r="C14" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="F10" s="15" t="s">
+      <c r="D14" s="29" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="E14" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H30" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="24"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="24"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="24"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="24"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="24"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="24"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="24"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="24"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="24"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="24"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="24"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="24"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="24"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
+      <c r="F14" s="29" t="s">
+        <v>531</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -5083,6 +4514,1696 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.36328125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="35.08984375" style="26" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="32.26953125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>558</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
+        <v>557</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>555</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>546</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>551</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="F40" s="26" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D47" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>546</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D54" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>544</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="34" t="s">
+        <v>561</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -5095,479 +6216,479 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B4" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="C5" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="B6" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="D8" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D10" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E10" s="16" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="B11" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D11" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="B12" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="E13" s="16" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="D14" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="E14" s="17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="B16" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="E16" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="B17" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="E17" s="16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C18" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="E18" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="19" t="s">
+      <c r="E19" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="E20" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="D10" s="19" t="s">
+      <c r="C21" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="D21" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="E21" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="D11" s="19" t="s">
+    </row>
+    <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="D13" s="19" t="s">
+      <c r="E22" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="19" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="D14" s="19" t="s">
+      <c r="E24" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>467</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="D15" s="19" t="s">
+      <c r="E25" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="D27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="19" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="E27" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="D16" s="19" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="D28" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>343</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>355</v>
+      <c r="E28" s="16" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -5577,7 +6698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -5590,563 +6711,563 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="17" t="s">
+      <c r="E5" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="B6" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="B7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="D7" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="C8" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B9" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="C9" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>378</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="B10" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>382</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="B16" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B17" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="C17" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>389</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>393</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>397</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="C18" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>401</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>406</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="B12" s="19" t="s">
+      <c r="F19" s="19" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>416</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>470</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>472</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="C20" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>424</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="19" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="B21" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>427</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="D21" s="16" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="E21" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="B22" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="D22" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="E22" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+    <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B23" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="B25" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F19" s="22" t="s">
+      <c r="C25" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="19" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+    <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>442</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>443</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="C22" s="19" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="19" t="s">
         <v>444</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>447</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>451</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>462</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -6155,7 +7276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -6169,28 +7290,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6201,22 +7322,22 @@
         <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>540</v>
+        <v>119</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>525</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -6227,20 +7348,20 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H3" s="29"/>
+        <v>120</v>
+      </c>
+      <c r="H3" s="24"/>
       <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -6251,20 +7372,20 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" s="29"/>
+        <v>121</v>
+      </c>
+      <c r="H4" s="24"/>
       <c r="I4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6275,20 +7396,20 @@
         <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H5" s="29"/>
+        <v>122</v>
+      </c>
+      <c r="H5" s="24"/>
       <c r="I5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6299,20 +7420,20 @@
         <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H6" s="29"/>
+        <v>132</v>
+      </c>
+      <c r="H6" s="24"/>
       <c r="I6" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6323,20 +7444,20 @@
         <v>37</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="H7" s="29"/>
+        <v>133</v>
+      </c>
+      <c r="H7" s="24"/>
       <c r="I7" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -6347,20 +7468,20 @@
         <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H8" s="29"/>
+        <v>125</v>
+      </c>
+      <c r="H8" s="24"/>
       <c r="I8" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -6371,20 +7492,20 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H9" s="29"/>
+        <v>126</v>
+      </c>
+      <c r="H9" s="24"/>
       <c r="I9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -6395,20 +7516,20 @@
         <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H10" s="28"/>
+        <v>127</v>
+      </c>
+      <c r="H10" s="25"/>
       <c r="I10" s="5" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -6419,22 +7540,22 @@
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="27" t="s">
-        <v>541</v>
+        <v>123</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>526</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -6445,20 +7566,20 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="H12" s="29"/>
+        <v>119</v>
+      </c>
+      <c r="H12" s="24"/>
       <c r="I12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6469,20 +7590,20 @@
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H13" s="29"/>
+        <v>124</v>
+      </c>
+      <c r="H13" s="24"/>
       <c r="I13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -6493,20 +7614,20 @@
         <v>26</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H14" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="H14" s="24"/>
       <c r="I14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6517,20 +7638,20 @@
         <v>27</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H15" s="28"/>
+        <v>130</v>
+      </c>
+      <c r="H15" s="25"/>
       <c r="I15" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -6541,22 +7662,22 @@
         <v>33</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>542</v>
+        <v>131</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>527</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>33</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6567,20 +7688,20 @@
         <v>21</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H17" s="29"/>
+        <v>129</v>
+      </c>
+      <c r="H17" s="24"/>
       <c r="I17" s="5" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -6591,20 +7712,20 @@
         <v>21</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H18" s="29"/>
+        <v>129</v>
+      </c>
+      <c r="H18" s="24"/>
       <c r="I18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -6615,20 +7736,20 @@
         <v>18</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" s="29"/>
+        <v>128</v>
+      </c>
+      <c r="H19" s="24"/>
       <c r="I19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6639,20 +7760,20 @@
         <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H20" s="29"/>
+        <v>130</v>
+      </c>
+      <c r="H20" s="24"/>
       <c r="I20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6663,20 +7784,20 @@
         <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="28"/>
+        <v>130</v>
+      </c>
+      <c r="H21" s="25"/>
       <c r="I21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6687,22 +7808,22 @@
         <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>543</v>
+        <v>125</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>528</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6713,20 +7834,20 @@
         <v>38</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H23" s="29"/>
+        <v>132</v>
+      </c>
+      <c r="H23" s="24"/>
       <c r="I23" s="5" t="s">
         <v>38</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -6737,20 +7858,20 @@
         <v>38</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="29"/>
+        <v>133</v>
+      </c>
+      <c r="H24" s="24"/>
       <c r="I24" s="5" t="s">
         <v>38</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -6761,20 +7882,20 @@
         <v>30</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" s="28"/>
+        <v>130</v>
+      </c>
+      <c r="H25" s="25"/>
       <c r="I25" s="5" t="s">
         <v>30</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -6785,22 +7906,22 @@
         <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>544</v>
+        <v>129</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>529</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -6811,20 +7932,20 @@
         <v>31</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H27" s="28"/>
+        <v>130</v>
+      </c>
+      <c r="H27" s="25"/>
       <c r="I27" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -6843,7 +7964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -6857,42 +7978,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="84" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>515</v>
+        <v>143</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -6901,7 +8022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -6914,44 +8035,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -6962,86 +8083,86 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>510</v>
+        <v>155</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>495</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>511</v>
+        <v>157</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>496</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>514</v>
+        <v>159</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>499</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>512</v>
+        <v>161</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>497</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>513</v>
+        <v>163</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>498</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -7055,55 +8176,55 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -7114,58 +8235,58 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -7176,58 +8297,58 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -7238,16 +8359,16 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -7258,73 +8379,73 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D34" s="8"/>
     </row>
@@ -7336,109 +8457,109 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D43" s="8"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D44" s="8"/>
     </row>
@@ -7450,61 +8571,61 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D50" s="8"/>
     </row>
@@ -7516,73 +8637,73 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D52" s="8"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D57" s="8"/>
     </row>
@@ -7594,25 +8715,25 @@
     </row>
     <row r="59" spans="1:4" ht="28" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D59" s="8"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D60" s="8"/>
     </row>
@@ -7624,73 +8745,73 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D64" s="8"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D65" s="8"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D66" s="8"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D67" s="8"/>
     </row>

--- a/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
+++ b/Documents/HBase/Moment冷热分离测试/Moment_Testing_Engineering - 修改后.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="需求与风险" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="560">
   <si>
     <t>需求 ID</t>
   </si>
@@ -386,51 +386,6 @@
     <t>自动化脚本方法名</t>
   </si>
   <si>
-    <t>testTC_STT_01_StandardMigration</t>
-  </si>
-  <si>
-    <t>testTC_DT_01_HBaseWriteException</t>
-  </si>
-  <si>
-    <t>testTC_DT_02_HBaseFalseSuccess</t>
-  </si>
-  <si>
-    <t>testTC_DT_03_MySQLDeleteTimeout</t>
-  </si>
-  <si>
-    <t>testTC_STT_03_MigrationExceptionRollback</t>
-  </si>
-  <si>
-    <t>testTC_BVA_01_CommentCountZero</t>
-  </si>
-  <si>
-    <t>testTC_STT_02_HotMomentSkip</t>
-  </si>
-  <si>
-    <t>testTC_DT_05_CommentThresholdUnlock</t>
-  </si>
-  <si>
-    <t>testTC_BVA_04_CommentCount2001</t>
-  </si>
-  <si>
-    <t>testTC_STT_08_AccessTimeUpdate</t>
-  </si>
-  <si>
-    <t>testTC_STT_07_ListQueryRestore</t>
-  </si>
-  <si>
-    <t>testTC_STT_06_UserActiveRestore</t>
-  </si>
-  <si>
-    <t>testTC_STT_04_ConcurrentProtection</t>
-  </si>
-  <si>
-    <t>testTC_STT_05_InterruptedRecovery</t>
-  </si>
-  <si>
-    <t>testTC_DT_04_IdempotentRecovery</t>
-  </si>
-  <si>
     <t>缺陷ID</t>
   </si>
   <si>
@@ -533,15 +488,9 @@
     <t>最高优先级，必须覆盖</t>
   </si>
   <si>
-    <t>Risk Pri. &gt;= 12 或 Extensive测试</t>
-  </si>
-  <si>
     <t>中等优先级，建议覆盖</t>
   </si>
   <si>
-    <t>Risk Pri. 6-9</t>
-  </si>
-  <si>
     <t>低优先级，可选覆盖</t>
   </si>
   <si>
@@ -1083,9 +1032,6 @@
   </si>
   <si>
     <t xml:space="preserve">APPROVED 状态时间边界：169h（冷数据状态，执行迁移） </t>
-  </si>
-  <si>
-    <t>用例 ID</t>
   </si>
   <si>
     <t>关联 TCI ID</t>
@@ -2617,6 +2563,89 @@
   </si>
   <si>
     <t>条件/动作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.4.007</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统接收到与当前状态不匹配的事件，发生非法跳转或Crash</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>P0</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Risk Pri. &gt;= 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 或 Extensive测试</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk Pri. 6-9</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>非功能需求(需求文档未列出)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI-STT-Neg-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>负向路径</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TCI-STT-Neg-02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复审核拦截：验证 approved/rejected状态下不会接收管理员操作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复恢复拦截：验证 pending/approved状态下不会接收恢复事件</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSK-1.4.007</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用例 ID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用例ID</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -3001,6 +3030,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3010,26 +3053,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3355,10 +3384,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>2</v>
@@ -3367,16 +3396,16 @@
         <v>3</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3384,16 +3413,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>6</v>
@@ -3416,16 +3445,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>8</v>
@@ -3454,10 +3483,10 @@
         <v>37</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>14</v>
@@ -3486,10 +3515,10 @@
         <v>13</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>14</v>
@@ -3509,19 +3538,19 @@
     </row>
     <row r="6" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>6</v>
@@ -3547,13 +3576,13 @@
         <v>25</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>14</v>
@@ -3579,13 +3608,13 @@
         <v>25</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>6</v>
@@ -3608,16 +3637,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>6</v>
@@ -3640,16 +3669,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>6</v>
@@ -3678,10 +3707,10 @@
         <v>26</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>6</v>
@@ -3710,10 +3739,10 @@
         <v>27</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>6</v>
@@ -3739,13 +3768,13 @@
         <v>25</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>6</v>
@@ -3768,7 +3797,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>33</v>
@@ -3777,7 +3806,7 @@
         <v>77</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>6</v>
@@ -3800,10 +3829,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>77</v>
@@ -3829,19 +3858,19 @@
     </row>
     <row r="16" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>77</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>6</v>
@@ -3870,10 +3899,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>6</v>
@@ -3902,10 +3931,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>6</v>
@@ -3931,13 +3960,13 @@
         <v>25</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>14</v>
@@ -3963,13 +3992,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>6</v>
@@ -3989,19 +4018,19 @@
     </row>
     <row r="21" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>8</v>
@@ -4024,16 +4053,16 @@
         <v>39</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>6</v>
@@ -4053,115 +4082,115 @@
     </row>
     <row r="23" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>19</v>
+        <v>547</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>20</v>
+        <v>551</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>22</v>
+        <v>545</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>23</v>
+        <v>546</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>14</v>
+        <v>548</v>
       </c>
       <c r="G23" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" s="12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J23" s="12">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>480</v>
+        <v>23</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G24" s="12">
+        <v>4</v>
+      </c>
+      <c r="H24" s="12">
         <v>3</v>
-      </c>
-      <c r="H24" s="12">
-        <v>4</v>
       </c>
       <c r="I24" s="12">
         <v>12</v>
       </c>
       <c r="J24" s="12">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>493</v>
+        <v>25</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>508</v>
+        <v>31</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G25" s="12">
         <v>3</v>
       </c>
       <c r="H25" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I25" s="12">
+        <v>12</v>
+      </c>
+      <c r="J25" s="12">
         <v>15</v>
-      </c>
-      <c r="J25" s="12">
-        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>492</v>
+        <v>456</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>6</v>
@@ -4176,20 +4205,40 @@
         <v>15</v>
       </c>
       <c r="J26" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="12">
+        <v>3</v>
+      </c>
+      <c r="H27" s="12">
+        <v>5</v>
+      </c>
+      <c r="I27" s="12">
+        <v>15</v>
+      </c>
+      <c r="J27" s="12">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="21"/>
@@ -4218,293 +4267,293 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" style="26" customWidth="1"/>
-    <col min="3" max="3" width="34.453125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="25.1796875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="34.1796875" style="26" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="26"/>
+    <col min="1" max="1" width="18.1796875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="34.453125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" style="23" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="28" t="s">
-        <v>532</v>
+      <c r="F1" s="25" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="F9" s="26" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C10" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D11" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="F11" s="26" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="29" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="D12" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D3" s="29" t="s">
+      <c r="F12" s="26" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="F13" s="26" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="F3" s="29" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="29" t="s">
+      <c r="B14" s="26" t="s">
+        <v>512</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>267</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>272</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>274</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>530</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>531</v>
+      <c r="F14" s="26" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -4518,51 +4567,52 @@
   <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="35.08984375" style="26" customWidth="1"/>
-    <col min="4" max="4" width="23.36328125" style="26" customWidth="1"/>
-    <col min="5" max="5" width="32.26953125" style="26" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="26"/>
+    <col min="1" max="1" width="15.36328125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="35.08984375" style="23" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="32.26953125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" style="23" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="33" t="s">
-        <v>560</v>
+      <c r="F1" s="32" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C2" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
@@ -4575,55 +4625,57 @@
         <v>61</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C4" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="B5" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="34" t="s">
         <v>55</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>50</v>
@@ -4632,62 +4684,65 @@
         <v>51</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
-        <v>557</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A7" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F7" s="26"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="B8" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C9" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
@@ -4697,51 +4752,53 @@
         <v>57</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>544</v>
-      </c>
+      <c r="B11" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>544</v>
-      </c>
+      <c r="B12" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
@@ -4751,75 +4808,78 @@
         <v>56</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D13" s="26" t="s">
         <v>49</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C14" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C15" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="B16" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="34" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>50</v>
@@ -4828,45 +4888,47 @@
         <v>51</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="B18" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F18" s="26"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="B19" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F19" s="26"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
@@ -4882,35 +4944,36 @@
         <v>55</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>544</v>
-      </c>
+      <c r="C21" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C22" s="26" t="s">
         <v>58</v>
@@ -4922,7 +4985,7 @@
         <v>59</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4930,58 +4993,60 @@
         <v>49</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="B24" s="32" t="s">
+      <c r="A24" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B24" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>544</v>
-      </c>
+      <c r="C24" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="B25" s="32" t="s">
+      <c r="A25" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>544</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>544</v>
-      </c>
+      <c r="C25" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>47</v>
@@ -4993,38 +5058,38 @@
         <v>49</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
-        <v>254</v>
+      <c r="A28" s="34" t="s">
+        <v>237</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C28" s="26" t="s">
         <v>50</v>
@@ -5033,188 +5098,198 @@
         <v>51</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A29" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B30" s="30" t="s">
+      <c r="A30" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F30" s="26"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F31" s="26"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F32" s="26"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C33" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F33" s="26"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A34" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F34" s="26"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B35" s="30" t="s">
+      <c r="A35" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C35" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F35" s="26"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B36" s="30" t="s">
+      <c r="A36" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C36" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B37" s="30" t="s">
+      <c r="A37" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E37" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C37" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F37" s="26"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A38" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F38" s="26"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
-        <v>251</v>
+      <c r="A39" s="34" t="s">
+        <v>234</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C39" s="26" t="s">
         <v>50</v>
@@ -5223,200 +5298,206 @@
         <v>51</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B41" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F42" s="26"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F43" s="26"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B44" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B43" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D43" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B44" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C44" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C44" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F44" s="26"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A45" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F45" s="26"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B46" s="30" t="s">
+      <c r="A46" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C46" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F46" s="26"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B47" s="30" t="s">
+      <c r="A47" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B47" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D47" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E47" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C47" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F47" s="26"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D48" s="26" t="s">
         <v>49</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="s">
-        <v>257</v>
+      <c r="A50" s="34" t="s">
+        <v>240</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C50" s="26" t="s">
         <v>50</v>
@@ -5425,113 +5506,119 @@
         <v>51</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B51" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D51" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E51" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A51" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F51" s="26"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B52" s="30" t="s">
+      <c r="A52" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F52" s="26"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F53" s="26"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F54" s="26"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B55" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="C52" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E52" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E53" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E55" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="C55" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F55" s="26"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="D56" s="30" t="s">
-        <v>544</v>
-      </c>
-      <c r="E56" s="30" t="s">
-        <v>544</v>
-      </c>
+      <c r="A56" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="F56" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -5556,34 +5643,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
-        <v>562</v>
+      <c r="A1" s="28" t="s">
+        <v>544</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -5595,7 +5682,7 @@
     </row>
     <row r="3" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>62</v>
@@ -5621,33 +5708,33 @@
     </row>
     <row r="4" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>62</v>
@@ -5673,7 +5760,7 @@
     </row>
     <row r="6" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>52</v>
@@ -5699,7 +5786,7 @@
     </row>
     <row r="7" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>52</v>
@@ -5714,7 +5801,7 @@
         <v>52</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>64</v>
@@ -5725,7 +5812,7 @@
     </row>
     <row r="8" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>52</v>
@@ -5760,8 +5847,8 @@
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
-        <v>561</v>
+      <c r="A10" s="27" t="s">
+        <v>543</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -5773,7 +5860,7 @@
     </row>
     <row r="11" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>52</v>
@@ -5799,7 +5886,7 @@
     </row>
     <row r="12" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>67</v>
@@ -5825,7 +5912,7 @@
     </row>
     <row r="13" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>52</v>
@@ -5851,7 +5938,7 @@
     </row>
     <row r="14" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>52</v>
@@ -5877,7 +5964,7 @@
     </row>
     <row r="15" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>52</v>
@@ -5903,7 +5990,7 @@
     </row>
     <row r="16" spans="1:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>52</v>
@@ -6205,10 +6292,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="87" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -6229,7 +6316,7 @@
         <v>71</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6237,16 +6324,16 @@
         <v>73</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6254,16 +6341,16 @@
         <v>74</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6271,10 +6358,10 @@
         <v>75</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>6</v>
@@ -6291,13 +6378,13 @@
         <v>77</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6305,16 +6392,16 @@
         <v>78</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="D6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6322,16 +6409,16 @@
         <v>79</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6339,16 +6426,16 @@
         <v>80</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6356,7 +6443,7 @@
         <v>81</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>82</v>
@@ -6365,7 +6452,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6373,322 +6460,356 @@
         <v>83</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>84</v>
+        <v>552</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>326</v>
+        <v>553</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>327</v>
+        <v>555</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>6</v>
+        <v>548</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>5</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>85</v>
+        <v>554</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>326</v>
+        <v>553</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>328</v>
+        <v>556</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>6</v>
+        <v>548</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>5</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>330</v>
+        <v>85</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>332</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>333</v>
+        <v>86</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>332</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="D28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D29" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>341</v>
+      <c r="E29" s="16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -6705,17 +6826,17 @@
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="4" max="4" width="39.36328125" customWidth="1"/>
+    <col min="5" max="5" width="43.90625" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>352</v>
+        <v>558</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>94</v>
@@ -6738,16 +6859,16 @@
         <v>73</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6758,16 +6879,16 @@
         <v>74</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -6778,16 +6899,16 @@
         <v>75</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6798,16 +6919,16 @@
         <v>76</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6818,16 +6939,16 @@
         <v>78</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6841,13 +6962,13 @@
         <v>104</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -6858,16 +6979,16 @@
         <v>80</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -6878,16 +6999,16 @@
         <v>81</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
@@ -6898,116 +7019,116 @@
         <v>83</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -7018,19 +7139,19 @@
         <v>84</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="29" thickBot="1" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>109</v>
       </c>
@@ -7038,16 +7159,16 @@
         <v>85</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.3">
@@ -7058,216 +7179,216 @@
         <v>86</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>114</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -7278,17 +7399,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="41.81640625" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" customWidth="1"/>
-    <col min="10" max="10" width="19.6328125" customWidth="1"/>
+    <col min="6" max="6" width="23.36328125" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>116</v>
       </c>
@@ -7301,20 +7421,17 @@
       <c r="D1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>118</v>
+      <c r="F1" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -7327,20 +7444,17 @@
       <c r="D2" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="G2" s="29" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -7353,18 +7467,15 @@
       <c r="D3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -7377,18 +7488,15 @@
       <c r="D4" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="G4" s="30"/>
+      <c r="H4" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -7401,18 +7509,15 @@
       <c r="D5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
@@ -7425,18 +7530,15 @@
       <c r="D6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="G6" s="30"/>
+      <c r="H6" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>35</v>
       </c>
@@ -7449,18 +7551,15 @@
       <c r="D7" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="G7" s="30"/>
+      <c r="H7" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -7473,18 +7572,15 @@
       <c r="D8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="G8" s="30"/>
+      <c r="H8" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -7497,18 +7593,15 @@
       <c r="D9" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="G9" s="30"/>
+      <c r="H9" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -7521,18 +7614,15 @@
       <c r="D10" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="G10" s="31"/>
+      <c r="H10" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
@@ -7545,20 +7635,17 @@
       <c r="D11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>526</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="G11" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -7571,18 +7658,15 @@
       <c r="D12" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H12" s="24"/>
-      <c r="I12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="G12" s="30"/>
+      <c r="H12" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>4</v>
       </c>
@@ -7595,18 +7679,15 @@
       <c r="D13" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="G13" s="30"/>
+      <c r="H13" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
@@ -7619,18 +7700,15 @@
       <c r="D14" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="G14" s="30"/>
+      <c r="H14" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
@@ -7643,18 +7721,15 @@
       <c r="D15" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="G15" s="31"/>
+      <c r="H15" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
@@ -7667,20 +7742,17 @@
       <c r="D16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="I16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="G16" s="29" t="s">
+        <v>509</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
@@ -7693,18 +7765,15 @@
       <c r="D17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="24"/>
-      <c r="I17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="G17" s="30"/>
+      <c r="H17" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>32</v>
       </c>
@@ -7717,18 +7786,15 @@
       <c r="D18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="24"/>
-      <c r="I18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="G18" s="30"/>
+      <c r="H18" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
@@ -7741,18 +7807,15 @@
       <c r="D19" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H19" s="24"/>
-      <c r="I19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="G19" s="30"/>
+      <c r="H19" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
@@ -7765,18 +7828,15 @@
       <c r="D20" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="G20" s="30"/>
+      <c r="H20" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
@@ -7789,18 +7849,15 @@
       <c r="D21" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" s="25"/>
-      <c r="I21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="G21" s="31"/>
+      <c r="H21" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
@@ -7813,20 +7870,17 @@
       <c r="D22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>528</v>
-      </c>
-      <c r="I22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="G22" s="29" t="s">
+        <v>510</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
@@ -7839,18 +7893,15 @@
       <c r="D23" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="G23" s="30"/>
+      <c r="H23" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>35</v>
       </c>
@@ -7863,18 +7914,15 @@
       <c r="D24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="G24" s="30"/>
+      <c r="H24" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
@@ -7887,18 +7935,15 @@
       <c r="D25" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="G25" s="31"/>
+      <c r="H25" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>19</v>
       </c>
@@ -7911,20 +7956,17 @@
       <c r="D26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>529</v>
-      </c>
-      <c r="I26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="G26" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -7937,14 +7979,11 @@
       <c r="D27" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27" s="25"/>
-      <c r="I27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="G27" s="31"/>
+      <c r="H27" s="5" t="s">
         <v>103</v>
       </c>
     </row>
@@ -7953,11 +7992,11 @@
     <sortCondition ref="B2:B27"/>
   </sortState>
   <mergeCells count="5">
-    <mergeCell ref="H2:H10"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="H16:H21"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G2:G10"/>
+    <mergeCell ref="G11:G15"/>
+    <mergeCell ref="G16:G21"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7978,42 +8017,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="84" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -8035,16 +8074,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -8052,13 +8091,13 @@
         <v>116</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8069,10 +8108,10 @@
         <v>66</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8086,10 +8125,10 @@
         <v>117</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>66</v>
@@ -8100,13 +8139,13 @@
         <v>66</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8114,13 +8153,13 @@
         <v>66</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8128,13 +8167,13 @@
         <v>66</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8142,13 +8181,13 @@
         <v>66</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -8156,13 +8195,13 @@
         <v>66</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -8176,10 +8215,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>66</v>
@@ -8193,10 +8232,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>168</v>
+        <v>152</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -8207,10 +8246,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>170</v>
+        <v>153</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -8221,10 +8260,10 @@
         <v>8</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -8238,10 +8277,10 @@
         <v>68</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>66</v>
@@ -8252,13 +8291,13 @@
         <v>66</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -8266,13 +8305,13 @@
         <v>66</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -8280,13 +8319,13 @@
         <v>66</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -8300,10 +8339,10 @@
         <v>92</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>66</v>
@@ -8314,13 +8353,13 @@
         <v>66</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -8328,13 +8367,13 @@
         <v>66</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -8342,13 +8381,13 @@
         <v>66</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -8359,16 +8398,16 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -8379,25 +8418,25 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="D30" s="8"/>
     </row>
@@ -8409,7 +8448,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="D31" s="8"/>
     </row>
@@ -8421,7 +8460,7 @@
         <v>72</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="D32" s="8"/>
     </row>
@@ -8433,7 +8472,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="D33" s="8"/>
     </row>
@@ -8445,7 +8484,7 @@
         <v>3</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="D34" s="8"/>
     </row>
@@ -8457,13 +8496,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D36" s="8"/>
     </row>
@@ -8475,7 +8514,7 @@
         <v>41</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D37" s="8"/>
     </row>
@@ -8487,7 +8526,7 @@
         <v>42</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D38" s="8"/>
     </row>
@@ -8499,7 +8538,7 @@
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="D39" s="8"/>
     </row>
@@ -8511,7 +8550,7 @@
         <v>44</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D40" s="8"/>
     </row>
@@ -8523,7 +8562,7 @@
         <v>45</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D41" s="8"/>
     </row>
@@ -8532,10 +8571,10 @@
         <v>66</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="D42" s="8"/>
     </row>
@@ -8544,10 +8583,10 @@
         <v>66</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="D43" s="8"/>
     </row>
@@ -8556,10 +8595,10 @@
         <v>66</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="D44" s="8"/>
     </row>
@@ -8571,13 +8610,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D46" s="8"/>
     </row>
@@ -8589,7 +8628,7 @@
         <v>69</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="D47" s="8"/>
     </row>
@@ -8601,7 +8640,7 @@
         <v>70</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D48" s="8"/>
     </row>
@@ -8613,7 +8652,7 @@
         <v>71</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="D49" s="8"/>
     </row>
@@ -8625,7 +8664,7 @@
         <v>72</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="D50" s="8"/>
     </row>
@@ -8637,13 +8676,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="D52" s="8"/>
     </row>
@@ -8655,7 +8694,7 @@
         <v>93</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="D53" s="8"/>
     </row>
@@ -8667,7 +8706,7 @@
         <v>94</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="D54" s="8"/>
     </row>
@@ -8679,7 +8718,7 @@
         <v>95</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="D55" s="8"/>
     </row>
@@ -8691,7 +8730,7 @@
         <v>96</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="D56" s="8"/>
     </row>
@@ -8703,7 +8742,7 @@
         <v>97</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="D57" s="8"/>
     </row>
@@ -8715,13 +8754,13 @@
     </row>
     <row r="59" spans="1:4" ht="28" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="D59" s="8"/>
     </row>
@@ -8733,7 +8772,7 @@
         <v>118</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D60" s="8"/>
     </row>
@@ -8745,13 +8784,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="D62" s="8"/>
     </row>
@@ -8760,10 +8799,10 @@
         <v>66</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="D63" s="8"/>
     </row>
@@ -8772,10 +8811,10 @@
         <v>66</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="D64" s="8"/>
     </row>
@@ -8784,10 +8823,10 @@
         <v>66</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="D65" s="8"/>
     </row>
@@ -8796,10 +8835,10 @@
         <v>66</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="D66" s="8"/>
     </row>
@@ -8808,10 +8847,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="D67" s="8"/>
     </row>
